--- a/research/traditional_assets/database/data/turkey/turkey_computers_peripherals.xlsx
+++ b/research/traditional_assets/database/data/turkey/turkey_computers_peripherals.xlsx
@@ -1260,7 +1260,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1397,22 +1397,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1747353785204355</v>
+        <v>0.1743322900741344</v>
       </c>
       <c r="C2">
-        <v>445.0056323744636</v>
+        <v>441.8925818024965</v>
       </c>
       <c r="D2">
-        <v>411.0056323744636</v>
+        <v>412.2945818024965</v>
       </c>
       <c r="E2">
-        <v>-54.8</v>
+        <v>-50.398</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>4.402</v>
       </c>
       <c r="G2">
         <v>34</v>
@@ -1433,28 +1433,28 @@
         <v>37.2</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.2214206</v>
       </c>
       <c r="N2">
-        <v>37.2</v>
+        <v>36.9785794</v>
       </c>
       <c r="O2">
-        <v>9.300000000000001</v>
+        <v>9.24464485</v>
       </c>
       <c r="P2">
-        <v>27.9</v>
+        <v>27.73393455</v>
       </c>
       <c r="Q2">
-        <v>30.2</v>
+        <v>30.03393455</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1747353785204355</v>
+        <v>0.1757121616910449</v>
       </c>
       <c r="T2">
-        <v>1.246903653332528</v>
+        <v>1.256349893130501</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1471,7 +1471,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>168.0060482177358</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1479,22 +1479,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1743322900741344</v>
+        <v>0.1739292016278334</v>
       </c>
       <c r="C3">
-        <v>441.8925818024965</v>
+        <v>438.7876411791704</v>
       </c>
       <c r="D3">
-        <v>412.2945818024965</v>
+        <v>413.5916411791704</v>
       </c>
       <c r="E3">
-        <v>-50.398</v>
+        <v>-45.996</v>
       </c>
       <c r="F3">
-        <v>4.402</v>
+        <v>8.804</v>
       </c>
       <c r="G3">
         <v>34</v>
@@ -1515,28 +1515,28 @@
         <v>37.2</v>
       </c>
       <c r="M3">
-        <v>0.2214206</v>
+        <v>0.4428412</v>
       </c>
       <c r="N3">
-        <v>36.9785794</v>
+        <v>36.75715880000001</v>
       </c>
       <c r="O3">
-        <v>9.24464485</v>
+        <v>9.189289700000002</v>
       </c>
       <c r="P3">
-        <v>27.73393455</v>
+        <v>27.5678691</v>
       </c>
       <c r="Q3">
-        <v>30.03393455</v>
+        <v>29.8678691</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1757121616910449</v>
+        <v>0.1767088792120749</v>
       </c>
       <c r="T3">
-        <v>1.256349893130501</v>
+        <v>1.265988913332516</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1553,7 +1553,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>168.0060482177358</v>
+        <v>84.00302410886793</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1561,22 +1561,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1739292016278334</v>
+        <v>0.1735261131815322</v>
       </c>
       <c r="C4">
-        <v>438.7876411791704</v>
+        <v>435.6908872865901</v>
       </c>
       <c r="D4">
-        <v>413.5916411791704</v>
+        <v>414.8968872865901</v>
       </c>
       <c r="E4">
-        <v>-45.996</v>
+        <v>-41.59399999999999</v>
       </c>
       <c r="F4">
-        <v>8.804</v>
+        <v>13.206</v>
       </c>
       <c r="G4">
         <v>34</v>
@@ -1597,28 +1597,28 @@
         <v>37.2</v>
       </c>
       <c r="M4">
-        <v>0.4428412</v>
+        <v>0.6642617999999999</v>
       </c>
       <c r="N4">
-        <v>36.75715880000001</v>
+        <v>36.5357382</v>
       </c>
       <c r="O4">
-        <v>9.189289700000002</v>
+        <v>9.133934550000001</v>
       </c>
       <c r="P4">
-        <v>27.5678691</v>
+        <v>27.40180365000001</v>
       </c>
       <c r="Q4">
-        <v>29.8678691</v>
+        <v>29.70180365000001</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1767088792120749</v>
+        <v>0.1777261476098271</v>
       </c>
       <c r="T4">
-        <v>1.265988913332516</v>
+        <v>1.275826676219107</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1635,7 +1635,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>84.00302410886793</v>
+        <v>56.00201607257863</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1643,22 +1643,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1735261131815322</v>
+        <v>0.1731230247352312</v>
       </c>
       <c r="C5">
-        <v>435.6908872865901</v>
+        <v>432.6023978791894</v>
       </c>
       <c r="D5">
-        <v>414.8968872865901</v>
+        <v>416.2103978791894</v>
       </c>
       <c r="E5">
-        <v>-41.59399999999999</v>
+        <v>-37.19199999999999</v>
       </c>
       <c r="F5">
-        <v>13.206</v>
+        <v>17.608</v>
       </c>
       <c r="G5">
         <v>34</v>
@@ -1679,28 +1679,28 @@
         <v>37.2</v>
       </c>
       <c r="M5">
-        <v>0.6642617999999999</v>
+        <v>0.8856824</v>
       </c>
       <c r="N5">
-        <v>36.5357382</v>
+        <v>36.3143176</v>
       </c>
       <c r="O5">
-        <v>9.133934550000001</v>
+        <v>9.078579400000001</v>
       </c>
       <c r="P5">
-        <v>27.40180365000001</v>
+        <v>27.2357382</v>
       </c>
       <c r="Q5">
-        <v>29.70180365000001</v>
+        <v>29.5357382</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1777261476098271</v>
+        <v>0.1787646090991991</v>
       </c>
       <c r="T5">
-        <v>1.275826676219107</v>
+        <v>1.285869392499169</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1717,7 +1717,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>56.00201607257863</v>
+        <v>42.00151205443397</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1725,22 +1725,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1731230247352312</v>
+        <v>0.1727199362889301</v>
       </c>
       <c r="C6">
-        <v>432.6023978791894</v>
+        <v>429.5222516991719</v>
       </c>
       <c r="D6">
-        <v>416.2103978791894</v>
+        <v>417.5322516991719</v>
       </c>
       <c r="E6">
-        <v>-37.19199999999999</v>
+        <v>-32.78999999999999</v>
       </c>
       <c r="F6">
-        <v>17.608</v>
+        <v>22.01</v>
       </c>
       <c r="G6">
         <v>34</v>
@@ -1761,28 +1761,28 @@
         <v>37.2</v>
       </c>
       <c r="M6">
-        <v>0.8856824</v>
+        <v>1.107103</v>
       </c>
       <c r="N6">
-        <v>36.3143176</v>
+        <v>36.092897</v>
       </c>
       <c r="O6">
-        <v>9.078579400000001</v>
+        <v>9.02322425</v>
       </c>
       <c r="P6">
-        <v>27.2357382</v>
+        <v>27.06967275</v>
       </c>
       <c r="Q6">
-        <v>29.5357382</v>
+        <v>29.36967275</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1787646090991991</v>
+        <v>0.1798249329357159</v>
       </c>
       <c r="T6">
-        <v>1.285869392499169</v>
+        <v>1.296123534385128</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1799,7 +1799,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>42.00151205443397</v>
+        <v>33.60120964354717</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1807,22 +1807,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1727199362889301</v>
+        <v>0.172316847842629</v>
       </c>
       <c r="C7">
-        <v>429.5222516991719</v>
+        <v>426.4505284922468</v>
       </c>
       <c r="D7">
-        <v>417.5322516991719</v>
+        <v>418.8625284922468</v>
       </c>
       <c r="E7">
-        <v>-32.78999999999999</v>
+        <v>-28.38799999999999</v>
       </c>
       <c r="F7">
-        <v>22.01</v>
+        <v>26.412</v>
       </c>
       <c r="G7">
         <v>34</v>
@@ -1843,28 +1843,28 @@
         <v>37.2</v>
       </c>
       <c r="M7">
-        <v>1.107103</v>
+        <v>1.3285236</v>
       </c>
       <c r="N7">
-        <v>36.092897</v>
+        <v>35.87147640000001</v>
       </c>
       <c r="O7">
-        <v>9.02322425</v>
+        <v>8.967869100000001</v>
       </c>
       <c r="P7">
-        <v>27.06967275</v>
+        <v>26.9036073</v>
       </c>
       <c r="Q7">
-        <v>29.36967275</v>
+        <v>29.20360730000001</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1798249329357159</v>
+        <v>0.1809078168538606</v>
       </c>
       <c r="T7">
-        <v>1.296123534385128</v>
+        <v>1.306595849502702</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1881,7 +1881,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>33.60120964354717</v>
+        <v>28.00100803628931</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1889,22 +1889,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.172316847842629</v>
+        <v>0.1719137593963279</v>
       </c>
       <c r="C8">
-        <v>426.4505284922468</v>
+        <v>423.3873090236643</v>
       </c>
       <c r="D8">
-        <v>418.8625284922468</v>
+        <v>420.2013090236643</v>
       </c>
       <c r="E8">
-        <v>-28.388</v>
+        <v>-23.986</v>
       </c>
       <c r="F8">
-        <v>26.412</v>
+        <v>30.814</v>
       </c>
       <c r="G8">
         <v>34</v>
@@ -1925,28 +1925,28 @@
         <v>37.2</v>
       </c>
       <c r="M8">
-        <v>1.3285236</v>
+        <v>1.5499442</v>
       </c>
       <c r="N8">
-        <v>35.87147640000001</v>
+        <v>35.6500558</v>
       </c>
       <c r="O8">
-        <v>8.967869100000001</v>
+        <v>8.912513950000001</v>
       </c>
       <c r="P8">
-        <v>26.9036073</v>
+        <v>26.73754185</v>
       </c>
       <c r="Q8">
-        <v>29.20360730000001</v>
+        <v>29.03754185</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1809078168538606</v>
+        <v>0.1820139885982021</v>
       </c>
       <c r="T8">
-        <v>1.306595849502702</v>
+        <v>1.317293375698074</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1963,7 +1963,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>28.00100803628931</v>
+        <v>24.00086403110513</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1971,22 +1971,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1719137593963279</v>
+        <v>0.1715106709500268</v>
       </c>
       <c r="C9">
-        <v>423.3873090236643</v>
+        <v>420.3326750945634</v>
       </c>
       <c r="D9">
-        <v>420.2013090236643</v>
+        <v>421.5486750945634</v>
       </c>
       <c r="E9">
-        <v>-23.98599999999999</v>
+        <v>-19.584</v>
       </c>
       <c r="F9">
-        <v>30.814</v>
+        <v>35.216</v>
       </c>
       <c r="G9">
         <v>34</v>
@@ -2007,28 +2007,28 @@
         <v>37.2</v>
       </c>
       <c r="M9">
-        <v>1.5499442</v>
+        <v>1.7713648</v>
       </c>
       <c r="N9">
-        <v>35.6500558</v>
+        <v>35.4286352</v>
       </c>
       <c r="O9">
-        <v>8.912513950000001</v>
+        <v>8.857158800000001</v>
       </c>
       <c r="P9">
-        <v>26.73754185</v>
+        <v>26.5714764</v>
       </c>
       <c r="Q9">
-        <v>29.03754185</v>
+        <v>28.8714764</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1820139885982021</v>
+        <v>0.183144207554377</v>
       </c>
       <c r="T9">
-        <v>1.317293375698074</v>
+        <v>1.328223456810736</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2045,7 +2045,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>24.00086403110512</v>
+        <v>21.00075602721698</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2053,22 +2053,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1715106709500268</v>
+        <v>0.1711075825037257</v>
       </c>
       <c r="C10">
-        <v>420.3326750945634</v>
+        <v>417.2867095586319</v>
       </c>
       <c r="D10">
-        <v>421.5486750945634</v>
+        <v>422.9047095586319</v>
       </c>
       <c r="E10">
-        <v>-19.584</v>
+        <v>-15.182</v>
       </c>
       <c r="F10">
-        <v>35.216</v>
+        <v>39.61799999999999</v>
       </c>
       <c r="G10">
         <v>34</v>
@@ -2089,28 +2089,28 @@
         <v>37.2</v>
       </c>
       <c r="M10">
-        <v>1.7713648</v>
+        <v>1.9927854</v>
       </c>
       <c r="N10">
-        <v>35.4286352</v>
+        <v>35.2072146</v>
       </c>
       <c r="O10">
-        <v>8.857158800000001</v>
+        <v>8.80180365</v>
       </c>
       <c r="P10">
-        <v>26.5714764</v>
+        <v>26.40541095</v>
       </c>
       <c r="Q10">
-        <v>28.8714764</v>
+        <v>28.70541095</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.183144207554377</v>
+        <v>0.1842992664876107</v>
       </c>
       <c r="T10">
-        <v>1.328223456810736</v>
+        <v>1.339393759486314</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2127,7 +2127,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>21.00075602721698</v>
+        <v>18.66733869085954</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2135,22 +2135,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1711075825037257</v>
+        <v>0.1707044940574246</v>
       </c>
       <c r="C11">
-        <v>417.2867095586319</v>
+        <v>414.2494963390902</v>
       </c>
       <c r="D11">
-        <v>422.9047095586319</v>
+        <v>424.2694963390902</v>
       </c>
       <c r="E11">
-        <v>-15.182</v>
+        <v>-10.78</v>
       </c>
       <c r="F11">
-        <v>39.61799999999999</v>
+        <v>44.02</v>
       </c>
       <c r="G11">
         <v>34</v>
@@ -2171,28 +2171,28 @@
         <v>37.2</v>
       </c>
       <c r="M11">
-        <v>1.9927854</v>
+        <v>2.214206</v>
       </c>
       <c r="N11">
-        <v>35.2072146</v>
+        <v>34.98579400000001</v>
       </c>
       <c r="O11">
-        <v>8.80180365</v>
+        <v>8.746448500000001</v>
       </c>
       <c r="P11">
-        <v>26.40541095</v>
+        <v>26.23934550000001</v>
       </c>
       <c r="Q11">
-        <v>28.70541095</v>
+        <v>28.53934550000001</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1842992664876107</v>
+        <v>0.1854799933971385</v>
       </c>
       <c r="T11">
-        <v>1.339393759486314</v>
+        <v>1.350812291110238</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2209,7 +2209,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>18.66733869085954</v>
+        <v>16.80060482177359</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2217,22 +2217,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1707044940574246</v>
+        <v>0.1703014056111236</v>
       </c>
       <c r="C12">
-        <v>414.2494963390902</v>
+        <v>411.2211204460053</v>
       </c>
       <c r="D12">
-        <v>424.2694963390902</v>
+        <v>425.6431204460054</v>
       </c>
       <c r="E12">
-        <v>-10.77999999999999</v>
+        <v>-6.378</v>
       </c>
       <c r="F12">
-        <v>44.02</v>
+        <v>48.422</v>
       </c>
       <c r="G12">
         <v>34</v>
@@ -2253,28 +2253,28 @@
         <v>37.2</v>
       </c>
       <c r="M12">
-        <v>2.214206</v>
+        <v>2.4356266</v>
       </c>
       <c r="N12">
-        <v>34.98579400000001</v>
+        <v>34.7643734</v>
       </c>
       <c r="O12">
-        <v>8.746448500000001</v>
+        <v>8.691093350000001</v>
       </c>
       <c r="P12">
-        <v>26.23934550000001</v>
+        <v>26.07328005</v>
       </c>
       <c r="Q12">
-        <v>28.53934550000001</v>
+        <v>28.37328005</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1854799933971385</v>
+        <v>0.1866872534956444</v>
       </c>
       <c r="T12">
-        <v>1.350812291110238</v>
+        <v>1.362487418950431</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2291,7 +2291,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>16.80060482177359</v>
+        <v>15.27327711070326</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2299,22 +2299,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1703014056111236</v>
+        <v>0.1698983171648225</v>
       </c>
       <c r="C13">
-        <v>411.2211204460053</v>
+        <v>408.2016679939424</v>
       </c>
       <c r="D13">
-        <v>425.6431204460054</v>
+        <v>427.0256679939424</v>
       </c>
       <c r="E13">
-        <v>-6.378</v>
+        <v>-1.975999999999999</v>
       </c>
       <c r="F13">
-        <v>48.422</v>
+        <v>52.824</v>
       </c>
       <c r="G13">
         <v>34</v>
@@ -2335,28 +2335,28 @@
         <v>37.2</v>
       </c>
       <c r="M13">
-        <v>2.4356266</v>
+        <v>2.6570472</v>
       </c>
       <c r="N13">
-        <v>34.7643734</v>
+        <v>34.5429528</v>
       </c>
       <c r="O13">
-        <v>8.691093350000001</v>
+        <v>8.6357382</v>
       </c>
       <c r="P13">
-        <v>26.07328005</v>
+        <v>25.9072146</v>
       </c>
       <c r="Q13">
-        <v>28.37328005</v>
+        <v>28.2072146</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1866872534956444</v>
+        <v>0.1879219513236619</v>
       </c>
       <c r="T13">
-        <v>1.362487418950431</v>
+        <v>1.374427890605173</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2373,7 +2373,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>15.27327711070326</v>
+        <v>14.00050401814465</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2381,22 +2381,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1698983171648225</v>
+        <v>0.1694952287185214</v>
       </c>
       <c r="C14">
-        <v>408.2016679939424</v>
+        <v>405.1912262199598</v>
       </c>
       <c r="D14">
-        <v>427.0256679939424</v>
+        <v>428.4172262199598</v>
       </c>
       <c r="E14">
-        <v>-1.975999999999999</v>
+        <v>2.426000000000002</v>
       </c>
       <c r="F14">
-        <v>52.824</v>
+        <v>57.226</v>
       </c>
       <c r="G14">
         <v>34</v>
@@ -2417,28 +2417,28 @@
         <v>37.2</v>
       </c>
       <c r="M14">
-        <v>2.6570472</v>
+        <v>2.8784678</v>
       </c>
       <c r="N14">
-        <v>34.5429528</v>
+        <v>34.3215322</v>
       </c>
       <c r="O14">
-        <v>8.6357382</v>
+        <v>8.58038305</v>
       </c>
       <c r="P14">
-        <v>25.9072146</v>
+        <v>25.74114915</v>
       </c>
       <c r="Q14">
-        <v>28.2072146</v>
+        <v>28.04114915</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1879219513236619</v>
+        <v>0.1891850330097947</v>
       </c>
       <c r="T14">
-        <v>1.374427890605173</v>
+        <v>1.386642855861173</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2455,7 +2455,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>14.00050401814465</v>
+        <v>12.92354217059507</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2463,22 +2463,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1694952287185214</v>
+        <v>0.1692496402722203</v>
       </c>
       <c r="C15">
-        <v>405.1912262199598</v>
+        <v>401.6415115787828</v>
       </c>
       <c r="D15">
-        <v>428.4172262199598</v>
+        <v>429.2695115787828</v>
       </c>
       <c r="E15">
-        <v>2.426000000000002</v>
+        <v>6.82800000000001</v>
       </c>
       <c r="F15">
-        <v>57.226</v>
+        <v>61.62800000000001</v>
       </c>
       <c r="G15">
         <v>34</v>
@@ -2499,45 +2499,45 @@
         <v>37.2</v>
       </c>
       <c r="M15">
-        <v>2.8784678</v>
+        <v>3.1923304</v>
       </c>
       <c r="N15">
-        <v>34.3215322</v>
+        <v>34.0076696</v>
       </c>
       <c r="O15">
-        <v>8.58038305</v>
+        <v>8.5019174</v>
       </c>
       <c r="P15">
-        <v>25.74114915</v>
+        <v>25.5057522</v>
       </c>
       <c r="Q15">
-        <v>28.04114915</v>
+        <v>27.8057522</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1891850330097947</v>
+        <v>0.1904774886886282</v>
       </c>
       <c r="T15">
-        <v>1.386642855861173</v>
+        <v>1.399141890076615</v>
       </c>
       <c r="U15">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V15">
         <v>0.25</v>
       </c>
       <c r="W15">
-        <v>0.03772499999999999</v>
+        <v>0.03885</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y15">
-        <v>12.92354217059507</v>
+        <v>11.65292915795934</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2545,22 +2545,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1692496402722203</v>
+        <v>0.1688578018259192</v>
       </c>
       <c r="C16">
-        <v>401.6415115787828</v>
+        <v>398.6063838612846</v>
       </c>
       <c r="D16">
-        <v>429.2695115787828</v>
+        <v>430.6363838612846</v>
       </c>
       <c r="E16">
-        <v>6.82800000000001</v>
+        <v>11.23</v>
       </c>
       <c r="F16">
-        <v>61.62800000000001</v>
+        <v>66.03</v>
       </c>
       <c r="G16">
         <v>34</v>
@@ -2581,28 +2581,28 @@
         <v>37.2</v>
       </c>
       <c r="M16">
-        <v>3.1923304</v>
+        <v>3.420354</v>
       </c>
       <c r="N16">
-        <v>34.0076696</v>
+        <v>33.779646</v>
       </c>
       <c r="O16">
-        <v>8.5019174</v>
+        <v>8.4449115</v>
       </c>
       <c r="P16">
-        <v>25.5057522</v>
+        <v>25.3347345</v>
       </c>
       <c r="Q16">
-        <v>27.8057522</v>
+        <v>27.6347345</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1904774886886282</v>
+        <v>0.1918003550893167</v>
       </c>
       <c r="T16">
-        <v>1.399141890076615</v>
+        <v>1.411935019214774</v>
       </c>
       <c r="U16">
         <v>0.0518</v>
@@ -2619,7 +2619,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>11.65292915795934</v>
+        <v>10.87606721409538</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2627,22 +2627,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1688578018259192</v>
+        <v>0.1684659633796181</v>
       </c>
       <c r="C17">
-        <v>398.6063838612846</v>
+        <v>395.5799886902356</v>
       </c>
       <c r="D17">
-        <v>430.6363838612846</v>
+        <v>432.0119886902356</v>
       </c>
       <c r="E17">
-        <v>11.23</v>
+        <v>15.63200000000001</v>
       </c>
       <c r="F17">
-        <v>66.03</v>
+        <v>70.432</v>
       </c>
       <c r="G17">
         <v>34</v>
@@ -2663,28 +2663,28 @@
         <v>37.2</v>
       </c>
       <c r="M17">
-        <v>3.420354</v>
+        <v>3.6483776</v>
       </c>
       <c r="N17">
-        <v>33.779646</v>
+        <v>33.5516224</v>
       </c>
       <c r="O17">
-        <v>8.4449115</v>
+        <v>8.3879056</v>
       </c>
       <c r="P17">
-        <v>25.3347345</v>
+        <v>25.1637168</v>
       </c>
       <c r="Q17">
-        <v>27.6347345</v>
+        <v>27.4637168</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1918003550893167</v>
+        <v>0.1931547183090692</v>
       </c>
       <c r="T17">
-        <v>1.411935019214774</v>
+        <v>1.425032746665746</v>
       </c>
       <c r="U17">
         <v>0.0518</v>
@@ -2701,7 +2701,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>10.87606721409538</v>
+        <v>10.19631301321442</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2709,22 +2709,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1684659633796181</v>
+        <v>0.168290874933317</v>
       </c>
       <c r="C18">
-        <v>395.5799886902356</v>
+        <v>391.7955065904415</v>
       </c>
       <c r="D18">
-        <v>432.0119886902356</v>
+        <v>432.6295065904415</v>
       </c>
       <c r="E18">
-        <v>15.63200000000001</v>
+        <v>20.03400000000001</v>
       </c>
       <c r="F18">
-        <v>70.432</v>
+        <v>74.834</v>
       </c>
       <c r="G18">
         <v>34</v>
@@ -2745,45 +2745,45 @@
         <v>37.2</v>
       </c>
       <c r="M18">
-        <v>3.6483776</v>
+        <v>4.003619</v>
       </c>
       <c r="N18">
-        <v>33.5516224</v>
+        <v>33.196381</v>
       </c>
       <c r="O18">
-        <v>8.3879056</v>
+        <v>8.299095250000001</v>
       </c>
       <c r="P18">
-        <v>25.1637168</v>
+        <v>24.89728575</v>
       </c>
       <c r="Q18">
-        <v>27.4637168</v>
+        <v>27.19728575</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1931547183090692</v>
+        <v>0.194541716787129</v>
       </c>
       <c r="T18">
-        <v>1.425032746665746</v>
+        <v>1.438446082007103</v>
       </c>
       <c r="U18">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V18">
         <v>0.25</v>
       </c>
       <c r="W18">
-        <v>0.03885</v>
+        <v>0.040125</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y18">
-        <v>10.19631301321442</v>
+        <v>9.291593430843443</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2791,22 +2791,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.168290874933317</v>
+        <v>0.1679117864870159</v>
       </c>
       <c r="C19">
-        <v>391.7955065904415</v>
+        <v>388.7365779858865</v>
       </c>
       <c r="D19">
-        <v>432.6295065904415</v>
+        <v>433.9725779858865</v>
       </c>
       <c r="E19">
-        <v>20.03400000000001</v>
+        <v>24.43600000000001</v>
       </c>
       <c r="F19">
-        <v>74.834</v>
+        <v>79.236</v>
       </c>
       <c r="G19">
         <v>34</v>
@@ -2827,28 +2827,28 @@
         <v>37.2</v>
       </c>
       <c r="M19">
-        <v>4.003619</v>
+        <v>4.239126</v>
       </c>
       <c r="N19">
-        <v>33.196381</v>
+        <v>32.960874</v>
       </c>
       <c r="O19">
-        <v>8.299095250000001</v>
+        <v>8.240218500000001</v>
       </c>
       <c r="P19">
-        <v>24.89728575</v>
+        <v>24.7206555</v>
       </c>
       <c r="Q19">
-        <v>27.19728575</v>
+        <v>27.0206555</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.194541716787129</v>
+        <v>0.1959625444963609</v>
       </c>
       <c r="T19">
-        <v>1.438446082007103</v>
+        <v>1.45218657186898</v>
       </c>
       <c r="U19">
         <v>0.0535</v>
@@ -2865,7 +2865,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>9.291593430843443</v>
+        <v>8.775393795796589</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2873,22 +2873,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1679117864870159</v>
+        <v>0.1675326980407149</v>
       </c>
       <c r="C20">
-        <v>388.7365779858864</v>
+        <v>385.6860143129684</v>
       </c>
       <c r="D20">
-        <v>433.9725779858864</v>
+        <v>435.3240143129684</v>
       </c>
       <c r="E20">
-        <v>24.43599999999999</v>
+        <v>28.83800000000001</v>
       </c>
       <c r="F20">
-        <v>79.23599999999999</v>
+        <v>83.63800000000001</v>
       </c>
       <c r="G20">
         <v>34</v>
@@ -2909,28 +2909,28 @@
         <v>37.2</v>
       </c>
       <c r="M20">
-        <v>4.239126</v>
+        <v>4.474633</v>
       </c>
       <c r="N20">
-        <v>32.960874</v>
+        <v>32.72536700000001</v>
       </c>
       <c r="O20">
-        <v>8.240218500000001</v>
+        <v>8.181341750000001</v>
       </c>
       <c r="P20">
-        <v>24.7206555</v>
+        <v>24.54402525</v>
       </c>
       <c r="Q20">
-        <v>27.0206555</v>
+        <v>26.84402525</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1959625444963609</v>
+        <v>0.1974184543712529</v>
       </c>
       <c r="T20">
-        <v>1.45218657186898</v>
+        <v>1.466266333085473</v>
       </c>
       <c r="U20">
         <v>0.0535</v>
@@ -2947,7 +2947,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>8.775393795796589</v>
+        <v>8.313530964438872</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2955,22 +2955,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1675326980407149</v>
+        <v>0.1671536095944138</v>
       </c>
       <c r="C21">
-        <v>385.6860143129684</v>
+        <v>382.6438939636439</v>
       </c>
       <c r="D21">
-        <v>435.3240143129684</v>
+        <v>436.6838939636439</v>
       </c>
       <c r="E21">
-        <v>28.83800000000001</v>
+        <v>33.24000000000001</v>
       </c>
       <c r="F21">
-        <v>83.63800000000001</v>
+        <v>88.04000000000001</v>
       </c>
       <c r="G21">
         <v>34</v>
@@ -2991,28 +2991,28 @@
         <v>37.2</v>
       </c>
       <c r="M21">
-        <v>4.474633</v>
+        <v>4.71014</v>
       </c>
       <c r="N21">
-        <v>32.72536700000001</v>
+        <v>32.48986</v>
       </c>
       <c r="O21">
-        <v>8.181341750000001</v>
+        <v>8.122465</v>
       </c>
       <c r="P21">
-        <v>24.54402525</v>
+        <v>24.367395</v>
       </c>
       <c r="Q21">
-        <v>26.84402525</v>
+        <v>26.667395</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1974184543712529</v>
+        <v>0.1989107619930172</v>
       </c>
       <c r="T21">
-        <v>1.466266333085473</v>
+        <v>1.480698088332377</v>
       </c>
       <c r="U21">
         <v>0.0535</v>
@@ -3029,7 +3029,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>8.313530964438872</v>
+        <v>7.897854416216928</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3037,22 +3037,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1671536095944138</v>
+        <v>0.1669005211481127</v>
       </c>
       <c r="C22">
-        <v>382.6438939636439</v>
+        <v>379.1545213181769</v>
       </c>
       <c r="D22">
-        <v>436.6838939636439</v>
+        <v>437.5965213181769</v>
       </c>
       <c r="E22">
-        <v>33.24000000000001</v>
+        <v>37.64200000000001</v>
       </c>
       <c r="F22">
-        <v>88.04000000000001</v>
+        <v>92.44200000000001</v>
       </c>
       <c r="G22">
         <v>34</v>
@@ -3073,45 +3073,45 @@
         <v>37.2</v>
       </c>
       <c r="M22">
-        <v>4.71014</v>
+        <v>5.0196006</v>
       </c>
       <c r="N22">
-        <v>32.48986</v>
+        <v>32.1803994</v>
       </c>
       <c r="O22">
-        <v>8.122465</v>
+        <v>8.04509985</v>
       </c>
       <c r="P22">
-        <v>24.367395</v>
+        <v>24.13529955</v>
       </c>
       <c r="Q22">
-        <v>26.667395</v>
+        <v>26.43529955</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1989107619930172</v>
+        <v>0.200440849554573</v>
       </c>
       <c r="T22">
-        <v>1.480698088332377</v>
+        <v>1.495495204471608</v>
       </c>
       <c r="U22">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V22">
         <v>0.25</v>
       </c>
       <c r="W22">
-        <v>0.040125</v>
+        <v>0.040725</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y22">
-        <v>7.897854416216928</v>
+        <v>7.410948193766651</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3119,22 +3119,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1669005211481127</v>
+        <v>0.1665274327018116</v>
       </c>
       <c r="C23">
-        <v>379.1545213181769</v>
+        <v>376.1048420177202</v>
       </c>
       <c r="D23">
-        <v>437.5965213181769</v>
+        <v>438.9488420177202</v>
       </c>
       <c r="E23">
-        <v>37.642</v>
+        <v>42.044</v>
       </c>
       <c r="F23">
-        <v>92.44199999999999</v>
+        <v>96.84399999999999</v>
       </c>
       <c r="G23">
         <v>34</v>
@@ -3155,28 +3155,28 @@
         <v>37.2</v>
       </c>
       <c r="M23">
-        <v>5.0196006</v>
+        <v>5.2586292</v>
       </c>
       <c r="N23">
-        <v>32.18039940000001</v>
+        <v>31.9413708</v>
       </c>
       <c r="O23">
-        <v>8.045099850000001</v>
+        <v>7.9853427</v>
       </c>
       <c r="P23">
-        <v>24.13529955000001</v>
+        <v>23.9560281</v>
       </c>
       <c r="Q23">
-        <v>26.43529955000001</v>
+        <v>26.2560281</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.200440849554573</v>
+        <v>0.2020101701305276</v>
       </c>
       <c r="T23">
-        <v>1.495495204471608</v>
+        <v>1.510671733845178</v>
       </c>
       <c r="U23">
         <v>0.0543</v>
@@ -3193,7 +3193,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>7.410948193766654</v>
+        <v>7.074086912231804</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3201,22 +3201,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1665274327018116</v>
+        <v>0.1661543442555105</v>
       </c>
       <c r="C24">
-        <v>376.1048420177202</v>
+        <v>373.0635468804077</v>
       </c>
       <c r="D24">
-        <v>438.9488420177202</v>
+        <v>440.3095468804077</v>
       </c>
       <c r="E24">
-        <v>42.044</v>
+        <v>46.446</v>
       </c>
       <c r="F24">
-        <v>96.84399999999999</v>
+        <v>101.246</v>
       </c>
       <c r="G24">
         <v>34</v>
@@ -3237,28 +3237,28 @@
         <v>37.2</v>
       </c>
       <c r="M24">
-        <v>5.2586292</v>
+        <v>5.4976578</v>
       </c>
       <c r="N24">
-        <v>31.9413708</v>
+        <v>31.7023422</v>
       </c>
       <c r="O24">
-        <v>7.9853427</v>
+        <v>7.925585550000001</v>
       </c>
       <c r="P24">
-        <v>23.9560281</v>
+        <v>23.77675665</v>
       </c>
       <c r="Q24">
-        <v>26.2560281</v>
+        <v>26.07675665</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.2020101701305276</v>
+        <v>0.2036202522798838</v>
       </c>
       <c r="T24">
-        <v>1.510671733845178</v>
+        <v>1.526242458786893</v>
       </c>
       <c r="U24">
         <v>0.0543</v>
@@ -3275,7 +3275,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>7.074086912231804</v>
+        <v>6.766517916047813</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3283,22 +3283,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1661543442555105</v>
+        <v>0.1657812558092094</v>
       </c>
       <c r="C25">
-        <v>373.0635468804077</v>
+        <v>370.0307141193168</v>
       </c>
       <c r="D25">
-        <v>440.3095468804077</v>
+        <v>441.6787141193169</v>
       </c>
       <c r="E25">
-        <v>46.446</v>
+        <v>50.84800000000001</v>
       </c>
       <c r="F25">
-        <v>101.246</v>
+        <v>105.648</v>
       </c>
       <c r="G25">
         <v>34</v>
@@ -3319,28 +3319,28 @@
         <v>37.2</v>
       </c>
       <c r="M25">
-        <v>5.4976578</v>
+        <v>5.736686400000001</v>
       </c>
       <c r="N25">
-        <v>31.7023422</v>
+        <v>31.4633136</v>
       </c>
       <c r="O25">
-        <v>7.925585550000001</v>
+        <v>7.865828400000001</v>
       </c>
       <c r="P25">
-        <v>23.77675665</v>
+        <v>23.5974852</v>
       </c>
       <c r="Q25">
-        <v>26.07675665</v>
+        <v>25.8974852</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.2036202522798838</v>
+        <v>0.2052727050121176</v>
       </c>
       <c r="T25">
-        <v>1.526242458786893</v>
+        <v>1.542222939648126</v>
       </c>
       <c r="U25">
         <v>0.0543</v>
@@ -3357,7 +3357,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>6.766517916047813</v>
+        <v>6.48457966954582</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3365,22 +3365,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1657812558092094</v>
+        <v>0.1654081673629083</v>
       </c>
       <c r="C26">
-        <v>370.0307141193168</v>
+        <v>367.006422923391</v>
       </c>
       <c r="D26">
-        <v>441.6787141193169</v>
+        <v>443.056422923391</v>
       </c>
       <c r="E26">
-        <v>50.848</v>
+        <v>55.25</v>
       </c>
       <c r="F26">
-        <v>105.648</v>
+        <v>110.05</v>
       </c>
       <c r="G26">
         <v>34</v>
@@ -3401,28 +3401,28 @@
         <v>37.2</v>
       </c>
       <c r="M26">
-        <v>5.7366864</v>
+        <v>5.975715</v>
       </c>
       <c r="N26">
-        <v>31.4633136</v>
+        <v>31.224285</v>
       </c>
       <c r="O26">
-        <v>7.865828400000001</v>
+        <v>7.80607125</v>
       </c>
       <c r="P26">
-        <v>23.5974852</v>
+        <v>23.41821375</v>
       </c>
       <c r="Q26">
-        <v>25.8974852</v>
+        <v>25.71821375</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.2052727050121176</v>
+        <v>0.2069692231505444</v>
       </c>
       <c r="T26">
-        <v>1.542222939648126</v>
+        <v>1.55862956666566</v>
       </c>
       <c r="U26">
         <v>0.0543</v>
@@ -3439,7 +3439,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>6.484579669545821</v>
+        <v>6.225196482763987</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3447,22 +3447,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1654081673629083</v>
+        <v>0.1652300789166072</v>
       </c>
       <c r="C27">
-        <v>367.006422923391</v>
+        <v>363.2650875624661</v>
       </c>
       <c r="D27">
-        <v>443.056422923391</v>
+        <v>443.7170875624661</v>
       </c>
       <c r="E27">
-        <v>55.25</v>
+        <v>59.652</v>
       </c>
       <c r="F27">
-        <v>110.05</v>
+        <v>114.452</v>
       </c>
       <c r="G27">
         <v>34</v>
@@ -3483,45 +3483,45 @@
         <v>37.2</v>
       </c>
       <c r="M27">
-        <v>5.975715</v>
+        <v>6.3291956</v>
       </c>
       <c r="N27">
-        <v>31.224285</v>
+        <v>30.8708044</v>
       </c>
       <c r="O27">
-        <v>7.80607125</v>
+        <v>7.717701100000001</v>
       </c>
       <c r="P27">
-        <v>23.41821375</v>
+        <v>23.15310330000001</v>
       </c>
       <c r="Q27">
-        <v>25.71821375</v>
+        <v>25.45310330000001</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.2069692231505444</v>
+        <v>0.2087115931305503</v>
       </c>
       <c r="T27">
-        <v>1.55862956666566</v>
+        <v>1.575479616035018</v>
       </c>
       <c r="U27">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V27">
         <v>0.25</v>
       </c>
       <c r="W27">
-        <v>0.040725</v>
+        <v>0.041475</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y27">
-        <v>6.225196482763987</v>
+        <v>5.877524151726328</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3529,22 +3529,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1652300789166072</v>
+        <v>0.1648644904703061</v>
       </c>
       <c r="C28">
-        <v>363.2650875624661</v>
+        <v>360.2255243393627</v>
       </c>
       <c r="D28">
-        <v>443.7170875624661</v>
+        <v>445.0795243393626</v>
       </c>
       <c r="E28">
-        <v>59.652</v>
+        <v>64.054</v>
       </c>
       <c r="F28">
-        <v>114.452</v>
+        <v>118.854</v>
       </c>
       <c r="G28">
         <v>34</v>
@@ -3565,28 +3565,28 @@
         <v>37.2</v>
       </c>
       <c r="M28">
-        <v>6.3291956</v>
+        <v>6.5726262</v>
       </c>
       <c r="N28">
-        <v>30.8708044</v>
+        <v>30.6273738</v>
       </c>
       <c r="O28">
-        <v>7.717701100000001</v>
+        <v>7.65684345</v>
       </c>
       <c r="P28">
-        <v>23.15310330000001</v>
+        <v>22.97053035</v>
       </c>
       <c r="Q28">
-        <v>25.45310330000001</v>
+        <v>25.27053035</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.2087115931305503</v>
+        <v>0.210501699274392</v>
       </c>
       <c r="T28">
-        <v>1.575479616035018</v>
+        <v>1.592791310592578</v>
       </c>
       <c r="U28">
         <v>0.0553</v>
@@ -3603,7 +3603,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>5.877524151726328</v>
+        <v>5.659838072032759</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3611,22 +3611,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1648644904703061</v>
+        <v>0.1644989020240051</v>
       </c>
       <c r="C29">
-        <v>360.2255243393627</v>
+        <v>357.1943536310333</v>
       </c>
       <c r="D29">
-        <v>445.0795243393626</v>
+        <v>446.4503536310333</v>
       </c>
       <c r="E29">
-        <v>64.054</v>
+        <v>68.45600000000002</v>
       </c>
       <c r="F29">
-        <v>118.854</v>
+        <v>123.256</v>
       </c>
       <c r="G29">
         <v>34</v>
@@ -3647,28 +3647,28 @@
         <v>37.2</v>
       </c>
       <c r="M29">
-        <v>6.5726262</v>
+        <v>6.816056800000001</v>
       </c>
       <c r="N29">
-        <v>30.6273738</v>
+        <v>30.3839432</v>
       </c>
       <c r="O29">
-        <v>7.65684345</v>
+        <v>7.5959858</v>
       </c>
       <c r="P29">
-        <v>22.97053035</v>
+        <v>22.7879574</v>
       </c>
       <c r="Q29">
-        <v>25.27053035</v>
+        <v>25.0879574</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.210501699274392</v>
+        <v>0.2123415305888959</v>
       </c>
       <c r="T29">
-        <v>1.592791310592578</v>
+        <v>1.610583885554515</v>
       </c>
       <c r="U29">
         <v>0.0553</v>
@@ -3685,7 +3685,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>5.659838072032759</v>
+        <v>5.457700998031589</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3693,22 +3693,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1644989020240051</v>
+        <v>0.1641333135777039</v>
       </c>
       <c r="C30">
-        <v>357.1943536310333</v>
+        <v>354.1716532230064</v>
       </c>
       <c r="D30">
-        <v>446.4503536310333</v>
+        <v>447.8296532230064</v>
       </c>
       <c r="E30">
-        <v>68.45600000000002</v>
+        <v>72.85800000000002</v>
       </c>
       <c r="F30">
-        <v>123.256</v>
+        <v>127.658</v>
       </c>
       <c r="G30">
         <v>34</v>
@@ -3729,28 +3729,28 @@
         <v>37.2</v>
       </c>
       <c r="M30">
-        <v>6.816056800000001</v>
+        <v>7.059487400000001</v>
       </c>
       <c r="N30">
-        <v>30.3839432</v>
+        <v>30.1405126</v>
       </c>
       <c r="O30">
-        <v>7.5959858</v>
+        <v>7.53512815</v>
       </c>
       <c r="P30">
-        <v>22.7879574</v>
+        <v>22.60538445</v>
       </c>
       <c r="Q30">
-        <v>25.0879574</v>
+        <v>24.90538445</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.2123415305888959</v>
+        <v>0.2142331881376112</v>
       </c>
       <c r="T30">
-        <v>1.610583885554515</v>
+        <v>1.628877659811154</v>
       </c>
       <c r="U30">
         <v>0.0553</v>
@@ -3767,7 +3767,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>5.457700998031589</v>
+        <v>5.269504411892568</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3775,22 +3775,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1641333135777039</v>
+        <v>0.1637677251314029</v>
       </c>
       <c r="C31">
-        <v>354.1716532230064</v>
+        <v>351.1575018650565</v>
       </c>
       <c r="D31">
-        <v>447.8296532230064</v>
+        <v>449.2175018650565</v>
       </c>
       <c r="E31">
-        <v>72.85799999999999</v>
+        <v>77.26000000000001</v>
       </c>
       <c r="F31">
-        <v>127.658</v>
+        <v>132.06</v>
       </c>
       <c r="G31">
         <v>34</v>
@@ -3811,28 +3811,28 @@
         <v>37.2</v>
       </c>
       <c r="M31">
-        <v>7.059487399999999</v>
+        <v>7.302918</v>
       </c>
       <c r="N31">
-        <v>30.1405126</v>
+        <v>29.897082</v>
       </c>
       <c r="O31">
-        <v>7.535128150000001</v>
+        <v>7.474270500000001</v>
       </c>
       <c r="P31">
-        <v>22.60538445</v>
+        <v>22.4228115</v>
       </c>
       <c r="Q31">
-        <v>24.90538445</v>
+        <v>24.7228115</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.2142331881376112</v>
+        <v>0.2161788930448612</v>
       </c>
       <c r="T31">
-        <v>1.628877659811154</v>
+        <v>1.647694113332269</v>
       </c>
       <c r="U31">
         <v>0.0553</v>
@@ -3849,7 +3849,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>5.26950441189257</v>
+        <v>5.093854264829484</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3857,22 +3857,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1637677251314029</v>
+        <v>0.1634021366851018</v>
       </c>
       <c r="C32">
-        <v>351.1575018650565</v>
+        <v>348.1519792861926</v>
       </c>
       <c r="D32">
-        <v>449.2175018650565</v>
+        <v>450.6139792861926</v>
       </c>
       <c r="E32">
-        <v>77.26000000000001</v>
+        <v>81.66199999999999</v>
       </c>
       <c r="F32">
-        <v>132.06</v>
+        <v>136.462</v>
       </c>
       <c r="G32">
         <v>34</v>
@@ -3893,28 +3893,28 @@
         <v>37.2</v>
       </c>
       <c r="M32">
-        <v>7.302918</v>
+        <v>7.5463486</v>
       </c>
       <c r="N32">
-        <v>29.897082</v>
+        <v>29.6536514</v>
       </c>
       <c r="O32">
-        <v>7.474270500000001</v>
+        <v>7.41341285</v>
       </c>
       <c r="P32">
-        <v>22.4228115</v>
+        <v>22.24023855</v>
       </c>
       <c r="Q32">
-        <v>24.7228115</v>
+        <v>24.54023855</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.2161788930448612</v>
+        <v>0.2181809951957997</v>
       </c>
       <c r="T32">
-        <v>1.647694113332269</v>
+        <v>1.667055971303271</v>
       </c>
       <c r="U32">
         <v>0.0553</v>
@@ -3931,7 +3931,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>5.093854264829484</v>
+        <v>4.929536385318855</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3939,22 +3939,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1634021366851018</v>
+        <v>0.1630365482388007</v>
       </c>
       <c r="C33">
-        <v>348.1519792861926</v>
+        <v>345.1551662099258</v>
       </c>
       <c r="D33">
-        <v>450.6139792861926</v>
+        <v>452.0191662099259</v>
       </c>
       <c r="E33">
-        <v>81.66199999999999</v>
+        <v>86.06400000000001</v>
       </c>
       <c r="F33">
-        <v>136.462</v>
+        <v>140.864</v>
       </c>
       <c r="G33">
         <v>34</v>
@@ -3975,28 +3975,28 @@
         <v>37.2</v>
       </c>
       <c r="M33">
-        <v>7.5463486</v>
+        <v>7.789779200000001</v>
       </c>
       <c r="N33">
-        <v>29.6536514</v>
+        <v>29.4102208</v>
       </c>
       <c r="O33">
-        <v>7.41341285</v>
+        <v>7.3525552</v>
       </c>
       <c r="P33">
-        <v>22.24023855</v>
+        <v>22.0576656</v>
       </c>
       <c r="Q33">
-        <v>24.54023855</v>
+        <v>24.3576656</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.2181809951957997</v>
+        <v>0.2202419827041187</v>
       </c>
       <c r="T33">
-        <v>1.667055971303271</v>
+        <v>1.686987295685185</v>
       </c>
       <c r="U33">
         <v>0.0553</v>
@@ -4013,7 +4013,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>4.929536385318855</v>
+        <v>4.77548837327764</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4021,22 +4021,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1630365482388007</v>
+        <v>0.1626709597924996</v>
       </c>
       <c r="C34">
-        <v>345.1551662099258</v>
+        <v>342.1671443698248</v>
       </c>
       <c r="D34">
-        <v>452.0191662099259</v>
+        <v>453.4331443698247</v>
       </c>
       <c r="E34">
-        <v>86.06400000000001</v>
+        <v>90.46599999999999</v>
       </c>
       <c r="F34">
-        <v>140.864</v>
+        <v>145.266</v>
       </c>
       <c r="G34">
         <v>34</v>
@@ -4057,28 +4057,28 @@
         <v>37.2</v>
       </c>
       <c r="M34">
-        <v>7.789779200000001</v>
+        <v>8.0332098</v>
       </c>
       <c r="N34">
-        <v>29.4102208</v>
+        <v>29.1667902</v>
       </c>
       <c r="O34">
-        <v>7.3525552</v>
+        <v>7.29169755</v>
       </c>
       <c r="P34">
-        <v>22.0576656</v>
+        <v>21.87509265</v>
       </c>
       <c r="Q34">
-        <v>24.3576656</v>
+        <v>24.17509265</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.2202419827041187</v>
+        <v>0.2223644922276113</v>
       </c>
       <c r="T34">
-        <v>1.686987295685185</v>
+        <v>1.707513584974021</v>
       </c>
       <c r="U34">
         <v>0.0553</v>
@@ -4095,7 +4095,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>4.77548837327764</v>
+        <v>4.630776604390439</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4103,22 +4103,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1626709597924996</v>
+        <v>0.1629428713461985</v>
       </c>
       <c r="C35">
-        <v>342.1671443698248</v>
+        <v>336.712637210257</v>
       </c>
       <c r="D35">
-        <v>453.4331443698247</v>
+        <v>452.380637210257</v>
       </c>
       <c r="E35">
-        <v>90.46599999999999</v>
+        <v>94.86800000000001</v>
       </c>
       <c r="F35">
-        <v>145.266</v>
+        <v>149.668</v>
       </c>
       <c r="G35">
         <v>34</v>
@@ -4139,45 +4139,45 @@
         <v>37.2</v>
       </c>
       <c r="M35">
-        <v>8.0332098</v>
+        <v>8.650810400000001</v>
       </c>
       <c r="N35">
-        <v>29.1667902</v>
+        <v>28.5491896</v>
       </c>
       <c r="O35">
-        <v>7.29169755</v>
+        <v>7.1372974</v>
       </c>
       <c r="P35">
-        <v>21.87509265</v>
+        <v>21.4118922</v>
       </c>
       <c r="Q35">
-        <v>24.17509265</v>
+        <v>23.7118922</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.2223644922276113</v>
+        <v>0.2245513202215129</v>
       </c>
       <c r="T35">
-        <v>1.707513584974021</v>
+        <v>1.728661883029186</v>
       </c>
       <c r="U35">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V35">
         <v>0.25</v>
       </c>
       <c r="W35">
-        <v>0.041475</v>
+        <v>0.04335</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y35">
-        <v>4.630776604390439</v>
+        <v>4.300175160468203</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4185,22 +4185,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1629428713461985</v>
+        <v>0.1625960328998974</v>
       </c>
       <c r="C36">
-        <v>336.712637210257</v>
+        <v>333.6540304184937</v>
       </c>
       <c r="D36">
-        <v>452.380637210257</v>
+        <v>453.7240304184937</v>
       </c>
       <c r="E36">
-        <v>94.86800000000001</v>
+        <v>99.27000000000002</v>
       </c>
       <c r="F36">
-        <v>149.668</v>
+        <v>154.07</v>
       </c>
       <c r="G36">
         <v>34</v>
@@ -4221,28 +4221,28 @@
         <v>37.2</v>
       </c>
       <c r="M36">
-        <v>8.650810400000001</v>
+        <v>8.905246000000002</v>
       </c>
       <c r="N36">
-        <v>28.5491896</v>
+        <v>28.294754</v>
       </c>
       <c r="O36">
-        <v>7.1372974</v>
+        <v>7.0736885</v>
       </c>
       <c r="P36">
-        <v>21.4118922</v>
+        <v>21.2210655</v>
       </c>
       <c r="Q36">
-        <v>23.7118922</v>
+        <v>23.5210655</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.2245513202215129</v>
+        <v>0.2268054352306114</v>
       </c>
       <c r="T36">
-        <v>1.728661883029186</v>
+        <v>1.750460897947587</v>
       </c>
       <c r="U36">
         <v>0.0578</v>
@@ -4259,7 +4259,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>4.300175160468203</v>
+        <v>4.177313013026254</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4267,22 +4267,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1625960328998974</v>
+        <v>0.1622491944535963</v>
       </c>
       <c r="C37">
-        <v>333.6540304184937</v>
+        <v>330.6034260936481</v>
       </c>
       <c r="D37">
-        <v>453.7240304184937</v>
+        <v>455.075426093648</v>
       </c>
       <c r="E37">
-        <v>99.27000000000002</v>
+        <v>103.672</v>
       </c>
       <c r="F37">
-        <v>154.07</v>
+        <v>158.472</v>
       </c>
       <c r="G37">
         <v>34</v>
@@ -4303,28 +4303,28 @@
         <v>37.2</v>
       </c>
       <c r="M37">
-        <v>8.905246000000002</v>
+        <v>9.159681600000001</v>
       </c>
       <c r="N37">
-        <v>28.294754</v>
+        <v>28.0403184</v>
       </c>
       <c r="O37">
-        <v>7.0736885</v>
+        <v>7.010079600000001</v>
       </c>
       <c r="P37">
-        <v>21.2210655</v>
+        <v>21.0302388</v>
       </c>
       <c r="Q37">
-        <v>23.5210655</v>
+        <v>23.3302388</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.2268054352306114</v>
+        <v>0.2291299913337443</v>
       </c>
       <c r="T37">
-        <v>1.750460897947587</v>
+        <v>1.772941132082188</v>
       </c>
       <c r="U37">
         <v>0.0578</v>
@@ -4341,7 +4341,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>4.177313013026254</v>
+        <v>4.061276540442192</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4349,22 +4349,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1622491944535964</v>
+        <v>0.1628736060072952</v>
       </c>
       <c r="C38">
-        <v>330.603426093648</v>
+        <v>323.7742833451825</v>
       </c>
       <c r="D38">
-        <v>455.075426093648</v>
+        <v>452.6482833451826</v>
       </c>
       <c r="E38">
-        <v>103.672</v>
+        <v>108.074</v>
       </c>
       <c r="F38">
-        <v>158.472</v>
+        <v>162.874</v>
       </c>
       <c r="G38">
         <v>34</v>
@@ -4385,45 +4385,45 @@
         <v>37.2</v>
       </c>
       <c r="M38">
-        <v>9.159681599999999</v>
+        <v>9.9841762</v>
       </c>
       <c r="N38">
-        <v>28.0403184</v>
+        <v>27.2158238</v>
       </c>
       <c r="O38">
-        <v>7.010079600000001</v>
+        <v>6.803955950000001</v>
       </c>
       <c r="P38">
-        <v>21.0302388</v>
+        <v>20.41186785</v>
       </c>
       <c r="Q38">
-        <v>23.3302388</v>
+        <v>22.71186785</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.2291299913337443</v>
+        <v>0.2315283428687226</v>
       </c>
       <c r="T38">
-        <v>1.772941132082188</v>
+        <v>1.796135024443284</v>
       </c>
       <c r="U38">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V38">
         <v>0.25</v>
       </c>
       <c r="W38">
-        <v>0.04335</v>
+        <v>0.045975</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y38">
-        <v>4.061276540442193</v>
+        <v>3.725895782969055</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4431,22 +4431,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1628736060072952</v>
+        <v>0.1625530175609942</v>
       </c>
       <c r="C39">
-        <v>323.7742833451825</v>
+        <v>320.6151960587889</v>
       </c>
       <c r="D39">
-        <v>452.6482833451826</v>
+        <v>453.8911960587889</v>
       </c>
       <c r="E39">
-        <v>108.074</v>
+        <v>112.476</v>
       </c>
       <c r="F39">
-        <v>162.874</v>
+        <v>167.276</v>
       </c>
       <c r="G39">
         <v>34</v>
@@ -4467,28 +4467,28 @@
         <v>37.2</v>
       </c>
       <c r="M39">
-        <v>9.9841762</v>
+        <v>10.2540188</v>
       </c>
       <c r="N39">
-        <v>27.2158238</v>
+        <v>26.9459812</v>
       </c>
       <c r="O39">
-        <v>6.803955950000001</v>
+        <v>6.736495300000001</v>
       </c>
       <c r="P39">
-        <v>20.41186785</v>
+        <v>20.2094859</v>
       </c>
       <c r="Q39">
-        <v>22.71186785</v>
+        <v>22.5094859</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.2315283428687226</v>
+        <v>0.2340040605822487</v>
       </c>
       <c r="T39">
-        <v>1.796135024443284</v>
+        <v>1.820077106880545</v>
       </c>
       <c r="U39">
         <v>0.0613</v>
@@ -4505,7 +4505,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>3.725895782969055</v>
+        <v>3.627845893943553</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4513,22 +4513,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1625530175609942</v>
+        <v>0.1622324291146931</v>
       </c>
       <c r="C40">
-        <v>320.6151960587889</v>
+        <v>317.4629533166306</v>
       </c>
       <c r="D40">
-        <v>453.8911960587889</v>
+        <v>455.1409533166306</v>
       </c>
       <c r="E40">
-        <v>112.476</v>
+        <v>116.878</v>
       </c>
       <c r="F40">
-        <v>167.276</v>
+        <v>171.678</v>
       </c>
       <c r="G40">
         <v>34</v>
@@ -4549,28 +4549,28 @@
         <v>37.2</v>
       </c>
       <c r="M40">
-        <v>10.2540188</v>
+        <v>10.5238614</v>
       </c>
       <c r="N40">
-        <v>26.9459812</v>
+        <v>26.6761386</v>
       </c>
       <c r="O40">
-        <v>6.736495300000001</v>
+        <v>6.66903465</v>
       </c>
       <c r="P40">
-        <v>20.2094859</v>
+        <v>20.00710395</v>
       </c>
       <c r="Q40">
-        <v>22.5094859</v>
+        <v>22.30710395</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.2340040605822487</v>
+        <v>0.2365609493683493</v>
       </c>
       <c r="T40">
-        <v>1.820077106880545</v>
+        <v>1.844804175627224</v>
       </c>
       <c r="U40">
         <v>0.0613</v>
@@ -4587,7 +4587,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>3.627845893943553</v>
+        <v>3.534824204355257</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4595,22 +4595,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1622324291146931</v>
+        <v>0.162751840668392</v>
       </c>
       <c r="C41">
-        <v>317.4629533166306</v>
+        <v>311.0395617048091</v>
       </c>
       <c r="D41">
-        <v>455.1409533166306</v>
+        <v>453.1195617048091</v>
       </c>
       <c r="E41">
-        <v>116.878</v>
+        <v>121.28</v>
       </c>
       <c r="F41">
-        <v>171.678</v>
+        <v>176.08</v>
       </c>
       <c r="G41">
         <v>34</v>
@@ -4631,45 +4631,45 @@
         <v>37.2</v>
       </c>
       <c r="M41">
-        <v>10.5238614</v>
+        <v>11.286728</v>
       </c>
       <c r="N41">
-        <v>26.6761386</v>
+        <v>25.913272</v>
       </c>
       <c r="O41">
-        <v>6.66903465</v>
+        <v>6.478318</v>
       </c>
       <c r="P41">
-        <v>20.00710395</v>
+        <v>19.434954</v>
       </c>
       <c r="Q41">
-        <v>22.30710395</v>
+        <v>21.734954</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.2365609493683493</v>
+        <v>0.2392030677806533</v>
       </c>
       <c r="T41">
-        <v>1.844804175627224</v>
+        <v>1.870355479998792</v>
       </c>
       <c r="U41">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V41">
         <v>0.25</v>
       </c>
       <c r="W41">
-        <v>0.045975</v>
+        <v>0.04807500000000001</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y41">
-        <v>3.534824204355257</v>
+        <v>3.295906484146689</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4677,22 +4677,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.162751840668392</v>
+        <v>0.1624522522220909</v>
       </c>
       <c r="C42">
-        <v>311.0395617048091</v>
+        <v>307.8012716451993</v>
       </c>
       <c r="D42">
-        <v>453.1195617048091</v>
+        <v>454.2832716451994</v>
       </c>
       <c r="E42">
-        <v>121.28</v>
+        <v>125.682</v>
       </c>
       <c r="F42">
-        <v>176.08</v>
+        <v>180.482</v>
       </c>
       <c r="G42">
         <v>34</v>
@@ -4713,28 +4713,28 @@
         <v>37.2</v>
       </c>
       <c r="M42">
-        <v>11.286728</v>
+        <v>11.5688962</v>
       </c>
       <c r="N42">
-        <v>25.913272</v>
+        <v>25.6311038</v>
       </c>
       <c r="O42">
-        <v>6.478318</v>
+        <v>6.40777595</v>
       </c>
       <c r="P42">
-        <v>19.434954</v>
+        <v>19.22332785</v>
       </c>
       <c r="Q42">
-        <v>21.734954</v>
+        <v>21.52332785</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.2392030677806533</v>
+        <v>0.2419347495289676</v>
       </c>
       <c r="T42">
-        <v>1.870355479998792</v>
+        <v>1.896772930281261</v>
       </c>
       <c r="U42">
         <v>0.0641</v>
@@ -4751,7 +4751,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>3.295906484146689</v>
+        <v>3.215518521118722</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4759,22 +4759,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1624522522220909</v>
+        <v>0.1621526637757898</v>
       </c>
       <c r="C43">
-        <v>307.8012716451993</v>
+        <v>304.5689742984624</v>
       </c>
       <c r="D43">
-        <v>454.2832716451994</v>
+        <v>455.4529742984624</v>
       </c>
       <c r="E43">
-        <v>125.682</v>
+        <v>130.084</v>
       </c>
       <c r="F43">
-        <v>180.482</v>
+        <v>184.884</v>
       </c>
       <c r="G43">
         <v>34</v>
@@ -4795,28 +4795,28 @@
         <v>37.2</v>
       </c>
       <c r="M43">
-        <v>11.5688962</v>
+        <v>11.8510644</v>
       </c>
       <c r="N43">
-        <v>25.6311038</v>
+        <v>25.3489356</v>
       </c>
       <c r="O43">
-        <v>6.40777595</v>
+        <v>6.3372339</v>
       </c>
       <c r="P43">
-        <v>19.22332785</v>
+        <v>19.0117017</v>
       </c>
       <c r="Q43">
-        <v>21.52332785</v>
+        <v>21.3117017</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.2419347495289676</v>
+        <v>0.2447606271996376</v>
       </c>
       <c r="T43">
-        <v>1.896772930281261</v>
+        <v>1.924101327125194</v>
       </c>
       <c r="U43">
         <v>0.0641</v>
@@ -4833,7 +4833,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>3.215518521118722</v>
+        <v>3.13895855633018</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4841,22 +4841,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1621526637757898</v>
+        <v>0.1618530753294887</v>
       </c>
       <c r="C44">
-        <v>304.5689742984624</v>
+        <v>301.3427160747651</v>
       </c>
       <c r="D44">
-        <v>455.4529742984624</v>
+        <v>456.6287160747651</v>
       </c>
       <c r="E44">
-        <v>130.084</v>
+        <v>134.486</v>
       </c>
       <c r="F44">
-        <v>184.884</v>
+        <v>189.286</v>
       </c>
       <c r="G44">
         <v>34</v>
@@ -4877,28 +4877,28 @@
         <v>37.2</v>
       </c>
       <c r="M44">
-        <v>11.8510644</v>
+        <v>12.1332326</v>
       </c>
       <c r="N44">
-        <v>25.3489356</v>
+        <v>25.0667674</v>
       </c>
       <c r="O44">
-        <v>6.337233900000001</v>
+        <v>6.266691850000001</v>
       </c>
       <c r="P44">
-        <v>19.0117017</v>
+        <v>18.80007555</v>
       </c>
       <c r="Q44">
-        <v>21.3117017</v>
+        <v>21.10007555</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.2447606271996376</v>
+        <v>0.2476856584727872</v>
       </c>
       <c r="T44">
-        <v>1.924101327125194</v>
+        <v>1.952388615086458</v>
       </c>
       <c r="U44">
         <v>0.0641</v>
@@ -4915,7 +4915,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>3.138958556330181</v>
+        <v>3.065959520136456</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4923,22 +4923,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1618530753294887</v>
+        <v>0.1641274868831876</v>
       </c>
       <c r="C45">
-        <v>301.3427160747651</v>
+        <v>288.1637052977475</v>
       </c>
       <c r="D45">
-        <v>456.6287160747651</v>
+        <v>447.8517052977475</v>
       </c>
       <c r="E45">
-        <v>134.486</v>
+        <v>138.888</v>
       </c>
       <c r="F45">
-        <v>189.286</v>
+        <v>193.688</v>
       </c>
       <c r="G45">
         <v>34</v>
@@ -4959,45 +4959,45 @@
         <v>37.2</v>
       </c>
       <c r="M45">
-        <v>12.1332326</v>
+        <v>13.9261672</v>
       </c>
       <c r="N45">
-        <v>25.0667674</v>
+        <v>23.2738328</v>
       </c>
       <c r="O45">
-        <v>6.266691850000001</v>
+        <v>5.8184582</v>
       </c>
       <c r="P45">
-        <v>18.80007555</v>
+        <v>17.4553746</v>
       </c>
       <c r="Q45">
-        <v>21.10007555</v>
+        <v>19.7553746</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.2476856584727872</v>
+        <v>0.2507151551485493</v>
       </c>
       <c r="T45">
-        <v>1.952388615086458</v>
+        <v>1.981686163332053</v>
       </c>
       <c r="U45">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V45">
         <v>0.25</v>
       </c>
       <c r="W45">
-        <v>0.04807500000000001</v>
+        <v>0.053925</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y45">
-        <v>3.065959520136456</v>
+        <v>2.671230315258602</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5005,22 +5005,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1641274868831876</v>
+        <v>0.1638863984368865</v>
       </c>
       <c r="C46">
-        <v>288.1637052977475</v>
+        <v>284.6760516850771</v>
       </c>
       <c r="D46">
-        <v>447.8517052977475</v>
+        <v>448.7660516850772</v>
       </c>
       <c r="E46">
-        <v>138.888</v>
+        <v>143.29</v>
       </c>
       <c r="F46">
-        <v>193.688</v>
+        <v>198.09</v>
       </c>
       <c r="G46">
         <v>34</v>
@@ -5041,28 +5041,28 @@
         <v>37.2</v>
       </c>
       <c r="M46">
-        <v>13.9261672</v>
+        <v>14.242671</v>
       </c>
       <c r="N46">
-        <v>23.2738328</v>
+        <v>22.957329</v>
       </c>
       <c r="O46">
-        <v>5.8184582</v>
+        <v>5.73933225</v>
       </c>
       <c r="P46">
-        <v>17.4553746</v>
+        <v>17.21799675</v>
       </c>
       <c r="Q46">
-        <v>19.7553746</v>
+        <v>19.51799675</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.2507151551485493</v>
+        <v>0.2538548153397936</v>
       </c>
       <c r="T46">
-        <v>1.981686163332053</v>
+        <v>2.012049076968397</v>
       </c>
       <c r="U46">
         <v>0.07190000000000001</v>
@@ -5079,7 +5079,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>2.671230315258602</v>
+        <v>2.611869641586188</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5087,22 +5087,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1638863984368865</v>
+        <v>0.1636453099905855</v>
       </c>
       <c r="C47">
-        <v>284.6760516850771</v>
+        <v>281.1921392200165</v>
       </c>
       <c r="D47">
-        <v>448.7660516850772</v>
+        <v>449.6841392200165</v>
       </c>
       <c r="E47">
-        <v>143.29</v>
+        <v>147.692</v>
       </c>
       <c r="F47">
-        <v>198.09</v>
+        <v>202.492</v>
       </c>
       <c r="G47">
         <v>34</v>
@@ -5123,28 +5123,28 @@
         <v>37.2</v>
       </c>
       <c r="M47">
-        <v>14.242671</v>
+        <v>14.5591748</v>
       </c>
       <c r="N47">
-        <v>22.957329</v>
+        <v>22.6408252</v>
       </c>
       <c r="O47">
-        <v>5.73933225</v>
+        <v>5.6602063</v>
       </c>
       <c r="P47">
-        <v>17.21799675</v>
+        <v>16.9806189</v>
       </c>
       <c r="Q47">
-        <v>19.51799675</v>
+        <v>19.2806189</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.2538548153397936</v>
+        <v>0.2571107592418249</v>
       </c>
       <c r="T47">
-        <v>2.012049076968397</v>
+        <v>2.043536542961643</v>
       </c>
       <c r="U47">
         <v>0.07190000000000001</v>
@@ -5161,7 +5161,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>2.611869641586188</v>
+        <v>2.555089866769097</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5169,22 +5169,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1636453099905855</v>
+        <v>0.1634042215442843</v>
       </c>
       <c r="C48">
-        <v>281.1921392200165</v>
+        <v>277.7119909106039</v>
       </c>
       <c r="D48">
-        <v>449.6841392200165</v>
+        <v>450.6059909106039</v>
       </c>
       <c r="E48">
-        <v>147.692</v>
+        <v>152.094</v>
       </c>
       <c r="F48">
-        <v>202.492</v>
+        <v>206.894</v>
       </c>
       <c r="G48">
         <v>34</v>
@@ -5205,28 +5205,28 @@
         <v>37.2</v>
       </c>
       <c r="M48">
-        <v>14.5591748</v>
+        <v>14.8756786</v>
       </c>
       <c r="N48">
-        <v>22.6408252</v>
+        <v>22.3243214</v>
       </c>
       <c r="O48">
-        <v>5.6602063</v>
+        <v>5.581080350000001</v>
       </c>
       <c r="P48">
-        <v>16.9806189</v>
+        <v>16.74324105</v>
       </c>
       <c r="Q48">
-        <v>19.2806189</v>
+        <v>19.04324105</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.2571107592418249</v>
+        <v>0.2604895689514798</v>
       </c>
       <c r="T48">
-        <v>2.043536542961643</v>
+        <v>2.076212215218784</v>
       </c>
       <c r="U48">
         <v>0.07190000000000001</v>
@@ -5243,7 +5243,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>2.555089866769097</v>
+        <v>2.50072625258252</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5251,22 +5251,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1634042215442843</v>
+        <v>0.1645671330979833</v>
       </c>
       <c r="C49">
-        <v>277.7119909106039</v>
+        <v>268.8978703236434</v>
       </c>
       <c r="D49">
-        <v>450.6059909106039</v>
+        <v>446.1938703236434</v>
       </c>
       <c r="E49">
-        <v>152.094</v>
+        <v>156.496</v>
       </c>
       <c r="F49">
-        <v>206.894</v>
+        <v>211.296</v>
       </c>
       <c r="G49">
         <v>34</v>
@@ -5287,45 +5287,45 @@
         <v>37.2</v>
       </c>
       <c r="M49">
-        <v>14.8756786</v>
+        <v>16.0162368</v>
       </c>
       <c r="N49">
-        <v>22.3243214</v>
+        <v>21.1837632</v>
       </c>
       <c r="O49">
-        <v>5.581080350000001</v>
+        <v>5.2959408</v>
       </c>
       <c r="P49">
-        <v>16.74324105</v>
+        <v>15.8878224</v>
       </c>
       <c r="Q49">
-        <v>19.04324105</v>
+        <v>18.1878224</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.2604895689514798</v>
+        <v>0.263998332880737</v>
       </c>
       <c r="T49">
-        <v>2.076212215218784</v>
+        <v>2.110144644101201</v>
       </c>
       <c r="U49">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V49">
         <v>0.25</v>
       </c>
       <c r="W49">
-        <v>0.053925</v>
+        <v>0.05685</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y49">
-        <v>2.50072625258252</v>
+        <v>2.322642981901966</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5333,22 +5333,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1645671330979833</v>
+        <v>0.1643552946516822</v>
       </c>
       <c r="C50">
-        <v>268.8978703236434</v>
+        <v>265.2931440052291</v>
       </c>
       <c r="D50">
-        <v>446.1938703236434</v>
+        <v>446.9911440052291</v>
       </c>
       <c r="E50">
-        <v>156.496</v>
+        <v>160.898</v>
       </c>
       <c r="F50">
-        <v>211.296</v>
+        <v>215.698</v>
       </c>
       <c r="G50">
         <v>34</v>
@@ -5369,28 +5369,28 @@
         <v>37.2</v>
       </c>
       <c r="M50">
-        <v>16.0162368</v>
+        <v>16.3499084</v>
       </c>
       <c r="N50">
-        <v>21.1837632</v>
+        <v>20.8500916</v>
       </c>
       <c r="O50">
-        <v>5.2959408</v>
+        <v>5.212522900000001</v>
       </c>
       <c r="P50">
-        <v>15.8878224</v>
+        <v>15.6375687</v>
       </c>
       <c r="Q50">
-        <v>18.1878224</v>
+        <v>17.9375687</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.263998332880737</v>
+        <v>0.2676446953954552</v>
       </c>
       <c r="T50">
-        <v>2.110144644101201</v>
+        <v>2.145407756469202</v>
       </c>
       <c r="U50">
         <v>0.07580000000000001</v>
@@ -5407,7 +5407,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>2.322642981901966</v>
+        <v>2.275242104720293</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5415,22 +5415,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1643552946516822</v>
+        <v>0.1641434562053811</v>
       </c>
       <c r="C51">
-        <v>265.2931440052291</v>
+        <v>261.6912719759051</v>
       </c>
       <c r="D51">
-        <v>446.9911440052291</v>
+        <v>447.7912719759051</v>
       </c>
       <c r="E51">
-        <v>160.898</v>
+        <v>165.3</v>
       </c>
       <c r="F51">
-        <v>215.698</v>
+        <v>220.1</v>
       </c>
       <c r="G51">
         <v>34</v>
@@ -5451,28 +5451,28 @@
         <v>37.2</v>
       </c>
       <c r="M51">
-        <v>16.3499084</v>
+        <v>16.68358</v>
       </c>
       <c r="N51">
-        <v>20.8500916</v>
+        <v>20.51642</v>
       </c>
       <c r="O51">
-        <v>5.212522900000001</v>
+        <v>5.129105000000001</v>
       </c>
       <c r="P51">
-        <v>15.6375687</v>
+        <v>15.387315</v>
       </c>
       <c r="Q51">
-        <v>17.9375687</v>
+        <v>17.68731500000001</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.2676446953954552</v>
+        <v>0.2714369124107622</v>
       </c>
       <c r="T51">
-        <v>2.145407756469202</v>
+        <v>2.182081393331924</v>
       </c>
       <c r="U51">
         <v>0.07580000000000001</v>
@@ -5489,7 +5489,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>2.275242104720293</v>
+        <v>2.229737262625887</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5497,22 +5497,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1641434562053811</v>
+        <v>0.16393161775908</v>
       </c>
       <c r="C52">
-        <v>261.6912719759051</v>
+        <v>258.0922695909555</v>
       </c>
       <c r="D52">
-        <v>447.7912719759051</v>
+        <v>448.5942695909555</v>
       </c>
       <c r="E52">
-        <v>165.3</v>
+        <v>169.702</v>
       </c>
       <c r="F52">
-        <v>220.1</v>
+        <v>224.502</v>
       </c>
       <c r="G52">
         <v>34</v>
@@ -5533,28 +5533,28 @@
         <v>37.2</v>
       </c>
       <c r="M52">
-        <v>16.68358</v>
+        <v>17.0172516</v>
       </c>
       <c r="N52">
-        <v>20.51642</v>
+        <v>20.1827484</v>
       </c>
       <c r="O52">
-        <v>5.129105000000001</v>
+        <v>5.0456871</v>
       </c>
       <c r="P52">
-        <v>15.387315</v>
+        <v>15.1370613</v>
       </c>
       <c r="Q52">
-        <v>17.68731500000001</v>
+        <v>17.4370613</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.2714369124107622</v>
+        <v>0.2753839137940408</v>
       </c>
       <c r="T52">
-        <v>2.182081393331924</v>
+        <v>2.220251913331899</v>
       </c>
       <c r="U52">
         <v>0.07580000000000001</v>
@@ -5571,7 +5571,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>2.229737262625887</v>
+        <v>2.186016924143027</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5579,22 +5579,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.16393161775908</v>
+        <v>0.1637197793127789</v>
       </c>
       <c r="C53">
-        <v>258.0922695909555</v>
+        <v>254.4961523160042</v>
       </c>
       <c r="D53">
-        <v>448.5942695909555</v>
+        <v>449.4001523160042</v>
       </c>
       <c r="E53">
-        <v>169.702</v>
+        <v>174.104</v>
       </c>
       <c r="F53">
-        <v>224.502</v>
+        <v>228.904</v>
       </c>
       <c r="G53">
         <v>34</v>
@@ -5615,28 +5615,28 @@
         <v>37.2</v>
       </c>
       <c r="M53">
-        <v>17.0172516</v>
+        <v>17.3509232</v>
       </c>
       <c r="N53">
-        <v>20.1827484</v>
+        <v>19.8490768</v>
       </c>
       <c r="O53">
-        <v>5.0456871</v>
+        <v>4.962269200000001</v>
       </c>
       <c r="P53">
-        <v>15.1370613</v>
+        <v>14.8868076</v>
       </c>
       <c r="Q53">
-        <v>17.4370613</v>
+        <v>17.1868076</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.2753839137940408</v>
+        <v>0.2794953735682894</v>
       </c>
       <c r="T53">
-        <v>2.220251913331899</v>
+        <v>2.260012871665206</v>
       </c>
       <c r="U53">
         <v>0.07580000000000001</v>
@@ -5653,7 +5653,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>2.186016924143027</v>
+        <v>2.143978137140277</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5661,22 +5661,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1637197793127789</v>
+        <v>0.1635079408664778</v>
       </c>
       <c r="C54">
-        <v>254.4961523160042</v>
+        <v>250.9029357280093</v>
       </c>
       <c r="D54">
-        <v>449.4001523160042</v>
+        <v>450.2089357280094</v>
       </c>
       <c r="E54">
-        <v>174.104</v>
+        <v>178.506</v>
       </c>
       <c r="F54">
-        <v>228.904</v>
+        <v>233.306</v>
       </c>
       <c r="G54">
         <v>34</v>
@@ -5697,28 +5697,28 @@
         <v>37.2</v>
       </c>
       <c r="M54">
-        <v>17.3509232</v>
+        <v>17.6845948</v>
       </c>
       <c r="N54">
-        <v>19.8490768</v>
+        <v>19.5154052</v>
       </c>
       <c r="O54">
-        <v>4.962269200000001</v>
+        <v>4.8788513</v>
       </c>
       <c r="P54">
-        <v>14.8868076</v>
+        <v>14.6365539</v>
       </c>
       <c r="Q54">
-        <v>17.1868076</v>
+        <v>16.9365539</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.2794953735682894</v>
+        <v>0.2837817890776124</v>
       </c>
       <c r="T54">
-        <v>2.260012871665206</v>
+        <v>2.301465785672272</v>
       </c>
       <c r="U54">
         <v>0.07580000000000001</v>
@@ -5735,7 +5735,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>2.143978137140277</v>
+        <v>2.103525719458384</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5743,22 +5743,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1635079408664778</v>
+        <v>0.1632961024201767</v>
       </c>
       <c r="C55">
-        <v>250.9029357280093</v>
+        <v>247.3126355162664</v>
       </c>
       <c r="D55">
-        <v>450.2089357280094</v>
+        <v>451.0206355162664</v>
       </c>
       <c r="E55">
-        <v>178.506</v>
+        <v>182.908</v>
       </c>
       <c r="F55">
-        <v>233.306</v>
+        <v>237.708</v>
       </c>
       <c r="G55">
         <v>34</v>
@@ -5779,28 +5779,28 @@
         <v>37.2</v>
       </c>
       <c r="M55">
-        <v>17.6845948</v>
+        <v>18.0182664</v>
       </c>
       <c r="N55">
-        <v>19.5154052</v>
+        <v>19.1817336</v>
       </c>
       <c r="O55">
-        <v>4.8788513</v>
+        <v>4.7954334</v>
       </c>
       <c r="P55">
-        <v>14.6365539</v>
+        <v>14.3863002</v>
       </c>
       <c r="Q55">
-        <v>16.9365539</v>
+        <v>16.6863002</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.2837817890776124</v>
+        <v>0.2882545704786451</v>
       </c>
       <c r="T55">
-        <v>2.301465785672272</v>
+        <v>2.34472100028834</v>
       </c>
       <c r="U55">
         <v>0.07580000000000001</v>
@@ -5817,7 +5817,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>2.103525719458384</v>
+        <v>2.064571539468414</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5825,22 +5825,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1632961024201767</v>
+        <v>0.1630842639738757</v>
       </c>
       <c r="C56">
-        <v>247.3126355162664</v>
+        <v>243.7252674834224</v>
       </c>
       <c r="D56">
-        <v>451.0206355162664</v>
+        <v>451.8352674834225</v>
       </c>
       <c r="E56">
-        <v>182.908</v>
+        <v>187.31</v>
       </c>
       <c r="F56">
-        <v>237.708</v>
+        <v>242.11</v>
       </c>
       <c r="G56">
         <v>34</v>
@@ -5861,28 +5861,28 @@
         <v>37.2</v>
       </c>
       <c r="M56">
-        <v>18.0182664</v>
+        <v>18.351938</v>
       </c>
       <c r="N56">
-        <v>19.1817336</v>
+        <v>18.848062</v>
       </c>
       <c r="O56">
-        <v>4.7954334</v>
+        <v>4.7120155</v>
       </c>
       <c r="P56">
-        <v>14.3863002</v>
+        <v>14.1360465</v>
       </c>
       <c r="Q56">
-        <v>16.6863002</v>
+        <v>16.4360465</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.2882545704786451</v>
+        <v>0.2929261421641681</v>
       </c>
       <c r="T56">
-        <v>2.34472100028834</v>
+        <v>2.389898668887345</v>
       </c>
       <c r="U56">
         <v>0.07580000000000001</v>
@@ -5899,7 +5899,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>2.064571539468414</v>
+        <v>2.027033875114443</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5907,22 +5907,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1630842639738757</v>
+        <v>0.1688364255275745</v>
       </c>
       <c r="C57">
-        <v>243.7252674834224</v>
+        <v>218.1992024508204</v>
       </c>
       <c r="D57">
-        <v>451.8352674834225</v>
+        <v>430.7112024508204</v>
       </c>
       <c r="E57">
-        <v>187.31</v>
+        <v>191.712</v>
       </c>
       <c r="F57">
-        <v>242.11</v>
+        <v>246.512</v>
       </c>
       <c r="G57">
         <v>34</v>
@@ -5943,45 +5943,45 @@
         <v>37.2</v>
       </c>
       <c r="M57">
-        <v>18.351938</v>
+        <v>22.18608</v>
       </c>
       <c r="N57">
-        <v>18.848062</v>
+        <v>15.01392</v>
       </c>
       <c r="O57">
-        <v>4.7120155</v>
+        <v>3.753480000000001</v>
       </c>
       <c r="P57">
-        <v>14.1360465</v>
+        <v>11.26044</v>
       </c>
       <c r="Q57">
-        <v>16.4360465</v>
+        <v>13.56044</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.2929261421641681</v>
+        <v>0.2978100580172149</v>
       </c>
       <c r="T57">
-        <v>2.389898668887345</v>
+        <v>2.437129867877213</v>
       </c>
       <c r="U57">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V57">
         <v>0.25</v>
       </c>
       <c r="W57">
-        <v>0.05685</v>
+        <v>0.0675</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y57">
-        <v>2.027033875114443</v>
+        <v>1.676727028839705</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5989,22 +5989,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1688364255275745</v>
+        <v>0.1687310870812735</v>
       </c>
       <c r="C58">
-        <v>218.1992024508204</v>
+        <v>214.1662746680101</v>
       </c>
       <c r="D58">
-        <v>430.7112024508204</v>
+        <v>431.0802746680101</v>
       </c>
       <c r="E58">
-        <v>191.712</v>
+        <v>196.114</v>
       </c>
       <c r="F58">
-        <v>246.512</v>
+        <v>250.914</v>
       </c>
       <c r="G58">
         <v>34</v>
@@ -6025,28 +6025,28 @@
         <v>37.2</v>
       </c>
       <c r="M58">
-        <v>22.18608</v>
+        <v>22.58226</v>
       </c>
       <c r="N58">
-        <v>15.01392</v>
+        <v>14.61774</v>
       </c>
       <c r="O58">
-        <v>3.753480000000001</v>
+        <v>3.654435</v>
       </c>
       <c r="P58">
-        <v>11.26044</v>
+        <v>10.963305</v>
       </c>
       <c r="Q58">
-        <v>13.56044</v>
+        <v>13.263305</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.2978100580172149</v>
+        <v>0.3029211327471476</v>
       </c>
       <c r="T58">
-        <v>2.437129867877213</v>
+        <v>2.486557866820099</v>
       </c>
       <c r="U58">
         <v>0.09</v>
@@ -6063,7 +6063,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>1.676727028839705</v>
+        <v>1.64731076517585</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6071,22 +6071,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1687310870812735</v>
+        <v>0.1686257486349724</v>
       </c>
       <c r="C59">
-        <v>214.1662746680101</v>
+        <v>210.1339799364023</v>
       </c>
       <c r="D59">
-        <v>431.0802746680101</v>
+        <v>431.4499799364024</v>
       </c>
       <c r="E59">
-        <v>196.114</v>
+        <v>200.516</v>
       </c>
       <c r="F59">
-        <v>250.914</v>
+        <v>255.316</v>
       </c>
       <c r="G59">
         <v>34</v>
@@ -6107,28 +6107,28 @@
         <v>37.2</v>
       </c>
       <c r="M59">
-        <v>22.58226</v>
+        <v>22.97844</v>
       </c>
       <c r="N59">
-        <v>14.61774</v>
+        <v>14.22156</v>
       </c>
       <c r="O59">
-        <v>3.654435</v>
+        <v>3.55539</v>
       </c>
       <c r="P59">
-        <v>10.963305</v>
+        <v>10.66617</v>
       </c>
       <c r="Q59">
-        <v>13.263305</v>
+        <v>12.96617</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.3029211327471476</v>
+        <v>0.3082755919880295</v>
       </c>
       <c r="T59">
-        <v>2.486557866820099</v>
+        <v>2.538339579998361</v>
       </c>
       <c r="U59">
         <v>0.09</v>
@@ -6145,7 +6145,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>1.64731076517585</v>
+        <v>1.618908855431439</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6153,22 +6153,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1686257486349724</v>
+        <v>0.1685204101886713</v>
       </c>
       <c r="C60">
-        <v>210.1339799364024</v>
+        <v>206.1023198861569</v>
       </c>
       <c r="D60">
-        <v>431.4499799364024</v>
+        <v>431.8203198861569</v>
       </c>
       <c r="E60">
-        <v>200.516</v>
+        <v>204.9179999999999</v>
       </c>
       <c r="F60">
-        <v>255.316</v>
+        <v>259.718</v>
       </c>
       <c r="G60">
         <v>34</v>
@@ -6189,28 +6189,28 @@
         <v>37.2</v>
       </c>
       <c r="M60">
-        <v>22.97844</v>
+        <v>23.37462</v>
       </c>
       <c r="N60">
-        <v>14.22156000000001</v>
+        <v>13.82538000000001</v>
       </c>
       <c r="O60">
-        <v>3.555390000000002</v>
+        <v>3.456345000000002</v>
       </c>
       <c r="P60">
-        <v>10.66617</v>
+        <v>10.369035</v>
       </c>
       <c r="Q60">
-        <v>12.96617000000001</v>
+        <v>12.669035</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.3082755919880295</v>
+        <v>0.3138912443626129</v>
       </c>
       <c r="T60">
-        <v>2.53833957999836</v>
+        <v>2.592647230404829</v>
       </c>
       <c r="U60">
         <v>0.09</v>
@@ -6227,7 +6227,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>1.61890885543144</v>
+        <v>1.591469722288534</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6235,22 +6235,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1685204101886713</v>
+        <v>0.1684150717423702</v>
       </c>
       <c r="C61">
-        <v>206.1023198861569</v>
+        <v>202.0712961530356</v>
       </c>
       <c r="D61">
-        <v>431.8203198861569</v>
+        <v>432.1912961530356</v>
       </c>
       <c r="E61">
-        <v>204.9179999999999</v>
+        <v>209.32</v>
       </c>
       <c r="F61">
-        <v>259.718</v>
+        <v>264.12</v>
       </c>
       <c r="G61">
         <v>34</v>
@@ -6271,28 +6271,28 @@
         <v>37.2</v>
       </c>
       <c r="M61">
-        <v>23.37462</v>
+        <v>23.7708</v>
       </c>
       <c r="N61">
-        <v>13.82538000000001</v>
+        <v>13.4292</v>
       </c>
       <c r="O61">
-        <v>3.456345000000002</v>
+        <v>3.3573</v>
       </c>
       <c r="P61">
-        <v>10.369035</v>
+        <v>10.0719</v>
       </c>
       <c r="Q61">
-        <v>12.669035</v>
+        <v>12.3719</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.3138912443626129</v>
+        <v>0.3197876793559255</v>
       </c>
       <c r="T61">
-        <v>2.592647230404829</v>
+        <v>2.649670263331621</v>
       </c>
       <c r="U61">
         <v>0.09</v>
@@ -6309,7 +6309,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>1.591469722288534</v>
+        <v>1.564945226917058</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6317,22 +6317,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1684150717423702</v>
+        <v>0.1683097332960691</v>
       </c>
       <c r="C62">
-        <v>202.0712961530356</v>
+        <v>198.0409103784261</v>
       </c>
       <c r="D62">
-        <v>432.1912961530356</v>
+        <v>432.5629103784261</v>
       </c>
       <c r="E62">
-        <v>209.32</v>
+        <v>213.722</v>
       </c>
       <c r="F62">
-        <v>264.12</v>
+        <v>268.522</v>
       </c>
       <c r="G62">
         <v>34</v>
@@ -6353,28 +6353,28 @@
         <v>37.2</v>
       </c>
       <c r="M62">
-        <v>23.7708</v>
+        <v>24.16698</v>
       </c>
       <c r="N62">
-        <v>13.4292</v>
+        <v>13.03302</v>
       </c>
       <c r="O62">
-        <v>3.3573</v>
+        <v>3.258255000000001</v>
       </c>
       <c r="P62">
-        <v>10.0719</v>
+        <v>9.774765000000002</v>
       </c>
       <c r="Q62">
-        <v>12.3719</v>
+        <v>12.074765</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.3197876793559255</v>
+        <v>0.3259864956309464</v>
       </c>
       <c r="T62">
-        <v>2.649670263331621</v>
+        <v>2.709617554357224</v>
       </c>
       <c r="U62">
         <v>0.09</v>
@@ -6391,7 +6391,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>1.564945226917058</v>
+        <v>1.539290387131532</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6399,22 +6399,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1683097332960691</v>
+        <v>0.168204394849768</v>
       </c>
       <c r="C63">
-        <v>198.0409103784261</v>
+        <v>194.0111642093663</v>
       </c>
       <c r="D63">
-        <v>432.5629103784261</v>
+        <v>432.9351642093662</v>
       </c>
       <c r="E63">
-        <v>213.722</v>
+        <v>218.124</v>
       </c>
       <c r="F63">
-        <v>268.522</v>
+        <v>272.924</v>
       </c>
       <c r="G63">
         <v>34</v>
@@ -6435,28 +6435,28 @@
         <v>37.2</v>
       </c>
       <c r="M63">
-        <v>24.16698</v>
+        <v>24.56316</v>
       </c>
       <c r="N63">
-        <v>13.03302</v>
+        <v>12.63684000000001</v>
       </c>
       <c r="O63">
-        <v>3.258255000000001</v>
+        <v>3.159210000000002</v>
       </c>
       <c r="P63">
-        <v>9.774765000000002</v>
+        <v>9.477630000000005</v>
       </c>
       <c r="Q63">
-        <v>12.074765</v>
+        <v>11.77763000000001</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.3259864956309464</v>
+        <v>0.3325115653941264</v>
       </c>
       <c r="T63">
-        <v>2.709617554357224</v>
+        <v>2.772719965963121</v>
       </c>
       <c r="U63">
         <v>0.09</v>
@@ -6473,7 +6473,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>1.539290387131532</v>
+        <v>1.514463122822959</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6481,22 +6481,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.168204394849768</v>
+        <v>0.1986828490868233</v>
       </c>
       <c r="C64">
-        <v>194.0111642093663</v>
+        <v>103.2999760382749</v>
       </c>
       <c r="D64">
-        <v>432.9351642093662</v>
+        <v>346.6259760382749</v>
       </c>
       <c r="E64">
-        <v>218.124</v>
+        <v>222.526</v>
       </c>
       <c r="F64">
-        <v>272.924</v>
+        <v>277.326</v>
       </c>
       <c r="G64">
         <v>34</v>
@@ -6517,45 +6517,45 @@
         <v>37.2</v>
       </c>
       <c r="M64">
-        <v>24.56316</v>
+        <v>40.71145680000001</v>
       </c>
       <c r="N64">
-        <v>12.63684000000001</v>
+        <v>-3.511456800000005</v>
       </c>
       <c r="O64">
-        <v>3.159210000000002</v>
+        <v>-0.8778642000000012</v>
       </c>
       <c r="P64">
-        <v>9.477630000000005</v>
+        <v>-2.633592600000004</v>
       </c>
       <c r="Q64">
-        <v>11.77763000000001</v>
+        <v>-0.3335926000000029</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.3325115653941264</v>
+        <v>0.3441232693248746</v>
       </c>
       <c r="T64">
-        <v>2.772719965963121</v>
+        <v>2.885014017594349</v>
       </c>
       <c r="U64">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V64">
-        <v>0.25</v>
+        <v>0.2284369249100415</v>
       </c>
       <c r="W64">
-        <v>0.0675</v>
+        <v>0.1132654594232059</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y64">
-        <v>1.514463122822959</v>
+        <v>0.9137476996401661</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6563,22 +6563,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1986828490868233</v>
+        <v>0.1996928490868233</v>
       </c>
       <c r="C65">
-        <v>103.2999760382749</v>
+        <v>96.62306698385134</v>
       </c>
       <c r="D65">
-        <v>346.6259760382749</v>
+        <v>344.3510669838514</v>
       </c>
       <c r="E65">
-        <v>222.526</v>
+        <v>226.928</v>
       </c>
       <c r="F65">
-        <v>277.326</v>
+        <v>281.728</v>
       </c>
       <c r="G65">
         <v>34</v>
@@ -6599,37 +6599,37 @@
         <v>37.2</v>
       </c>
       <c r="M65">
-        <v>40.71145680000001</v>
+        <v>41.3576704</v>
       </c>
       <c r="N65">
-        <v>-3.511456800000005</v>
+        <v>-4.157670400000001</v>
       </c>
       <c r="O65">
-        <v>-0.8778642000000012</v>
+        <v>-1.0394176</v>
       </c>
       <c r="P65">
-        <v>-2.633592600000004</v>
+        <v>-3.1182528</v>
       </c>
       <c r="Q65">
-        <v>-0.3335926000000029</v>
+        <v>-0.8182527999999998</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.3441232693248746</v>
+        <v>0.3524100268061211</v>
       </c>
       <c r="T65">
-        <v>2.885014017594349</v>
+        <v>2.965153295860858</v>
       </c>
       <c r="U65">
         <v>0.1468</v>
       </c>
       <c r="V65">
-        <v>0.2284369249100415</v>
+        <v>0.2248675979583221</v>
       </c>
       <c r="W65">
-        <v>0.1132654594232059</v>
+        <v>0.1137894366197183</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6637,7 +6637,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.9137476996401661</v>
+        <v>0.8994703918332886</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6645,22 +6645,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1996928490868233</v>
+        <v>0.2007028490868233</v>
       </c>
       <c r="C66">
-        <v>96.62306698385134</v>
+        <v>89.97582372522834</v>
       </c>
       <c r="D66">
-        <v>344.3510669838514</v>
+        <v>342.1058237252283</v>
       </c>
       <c r="E66">
-        <v>226.928</v>
+        <v>231.33</v>
       </c>
       <c r="F66">
-        <v>281.728</v>
+        <v>286.13</v>
       </c>
       <c r="G66">
         <v>34</v>
@@ -6681,37 +6681,37 @@
         <v>37.2</v>
       </c>
       <c r="M66">
-        <v>41.3576704</v>
+        <v>42.00388400000001</v>
       </c>
       <c r="N66">
-        <v>-4.157670400000001</v>
+        <v>-4.803884000000004</v>
       </c>
       <c r="O66">
-        <v>-1.0394176</v>
+        <v>-1.200971000000001</v>
       </c>
       <c r="P66">
-        <v>-3.1182528</v>
+        <v>-3.602913000000003</v>
       </c>
       <c r="Q66">
-        <v>-0.8182527999999998</v>
+        <v>-1.302913000000002</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.3524100268061211</v>
+        <v>0.3611703132862961</v>
       </c>
       <c r="T66">
-        <v>2.965153295860858</v>
+        <v>3.049871961456883</v>
       </c>
       <c r="U66">
         <v>0.1468</v>
       </c>
       <c r="V66">
-        <v>0.2248675979583221</v>
+        <v>0.221408096451271</v>
       </c>
       <c r="W66">
-        <v>0.1137894366197183</v>
+        <v>0.1142972914409534</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6719,7 +6719,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.8994703918332886</v>
+        <v>0.8856323858050841</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6727,22 +6727,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2007028490868233</v>
+        <v>0.2017128490868233</v>
       </c>
       <c r="C67">
-        <v>89.97582372522834</v>
+        <v>83.35766973929185</v>
       </c>
       <c r="D67">
-        <v>342.1058237252283</v>
+        <v>339.8896697392918</v>
       </c>
       <c r="E67">
-        <v>231.33</v>
+        <v>235.732</v>
       </c>
       <c r="F67">
-        <v>286.13</v>
+        <v>290.532</v>
       </c>
       <c r="G67">
         <v>34</v>
@@ -6763,37 +6763,37 @@
         <v>37.2</v>
       </c>
       <c r="M67">
-        <v>42.00388400000001</v>
+        <v>42.6500976</v>
       </c>
       <c r="N67">
-        <v>-4.803884000000004</v>
+        <v>-5.450097599999999</v>
       </c>
       <c r="O67">
-        <v>-1.200971000000001</v>
+        <v>-1.3625244</v>
       </c>
       <c r="P67">
-        <v>-3.602913000000003</v>
+        <v>-4.0875732</v>
       </c>
       <c r="Q67">
-        <v>-1.302913000000002</v>
+        <v>-1.787573199999999</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.3611703132862961</v>
+        <v>0.370445910735893</v>
       </c>
       <c r="T67">
-        <v>3.049871961456883</v>
+        <v>3.139574077970321</v>
       </c>
       <c r="U67">
         <v>0.1468</v>
       </c>
       <c r="V67">
-        <v>0.221408096451271</v>
+        <v>0.2180534283232215</v>
       </c>
       <c r="W67">
-        <v>0.1142972914409534</v>
+        <v>0.1147897567221511</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6801,7 +6801,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.8856323858050841</v>
+        <v>0.8722137132928859</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6809,22 +6809,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2017128490868233</v>
+        <v>0.2027228490868234</v>
       </c>
       <c r="C68">
-        <v>83.35766973929185</v>
+        <v>76.76804334559336</v>
       </c>
       <c r="D68">
-        <v>339.8896697392918</v>
+        <v>337.7020433455934</v>
       </c>
       <c r="E68">
-        <v>235.732</v>
+        <v>240.134</v>
       </c>
       <c r="F68">
-        <v>290.532</v>
+        <v>294.934</v>
       </c>
       <c r="G68">
         <v>34</v>
@@ -6845,37 +6845,37 @@
         <v>37.2</v>
       </c>
       <c r="M68">
-        <v>42.6500976</v>
+        <v>43.29631120000001</v>
       </c>
       <c r="N68">
-        <v>-5.450097599999999</v>
+        <v>-6.096311200000002</v>
       </c>
       <c r="O68">
-        <v>-1.3625244</v>
+        <v>-1.524077800000001</v>
       </c>
       <c r="P68">
-        <v>-4.0875732</v>
+        <v>-4.572233400000002</v>
       </c>
       <c r="Q68">
-        <v>-1.787573199999999</v>
+        <v>-2.272233400000001</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.370445910735893</v>
+        <v>0.3802836656066777</v>
       </c>
       <c r="T68">
-        <v>3.139574077970321</v>
+        <v>3.234712686393664</v>
       </c>
       <c r="U68">
         <v>0.1468</v>
       </c>
       <c r="V68">
-        <v>0.2180534283232215</v>
+        <v>0.2147988995422778</v>
       </c>
       <c r="W68">
-        <v>0.1147897567221511</v>
+        <v>0.1152675215471936</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6883,7 +6883,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.8722137132928859</v>
+        <v>0.8591955981691114</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6891,22 +6891,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2027228490868234</v>
+        <v>0.2037328490868233</v>
       </c>
       <c r="C69">
-        <v>76.76804334559336</v>
+        <v>70.20639723174702</v>
       </c>
       <c r="D69">
-        <v>337.7020433455934</v>
+        <v>335.542397231747</v>
       </c>
       <c r="E69">
-        <v>240.134</v>
+        <v>244.536</v>
       </c>
       <c r="F69">
-        <v>294.934</v>
+        <v>299.336</v>
       </c>
       <c r="G69">
         <v>34</v>
@@ -6927,37 +6927,37 @@
         <v>37.2</v>
       </c>
       <c r="M69">
-        <v>43.29631120000001</v>
+        <v>43.94252480000001</v>
       </c>
       <c r="N69">
-        <v>-6.096311200000002</v>
+        <v>-6.742524800000005</v>
       </c>
       <c r="O69">
-        <v>-1.524077800000001</v>
+        <v>-1.685631200000001</v>
       </c>
       <c r="P69">
-        <v>-4.572233400000002</v>
+        <v>-5.056893600000004</v>
       </c>
       <c r="Q69">
-        <v>-2.272233400000001</v>
+        <v>-2.756893600000003</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.3802836656066777</v>
+        <v>0.3907362801568863</v>
       </c>
       <c r="T69">
-        <v>3.234712686393664</v>
+        <v>3.335797457843465</v>
       </c>
       <c r="U69">
         <v>0.1468</v>
       </c>
       <c r="V69">
-        <v>0.2147988995422778</v>
+        <v>0.2116400921960679</v>
       </c>
       <c r="W69">
-        <v>0.1152675215471936</v>
+        <v>0.1157312344656172</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6965,7 +6965,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.8591955981691114</v>
+        <v>0.8465603687842715</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6973,22 +6973,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2037328490868233</v>
+        <v>0.2047428490868233</v>
       </c>
       <c r="C70">
-        <v>70.20639723174702</v>
+        <v>63.67219799692054</v>
       </c>
       <c r="D70">
-        <v>335.542397231747</v>
+        <v>333.4101979969205</v>
       </c>
       <c r="E70">
-        <v>244.536</v>
+        <v>248.938</v>
       </c>
       <c r="F70">
-        <v>299.336</v>
+        <v>303.738</v>
       </c>
       <c r="G70">
         <v>34</v>
@@ -7009,37 +7009,37 @@
         <v>37.2</v>
       </c>
       <c r="M70">
-        <v>43.94252480000001</v>
+        <v>44.5887384</v>
       </c>
       <c r="N70">
-        <v>-6.742524800000005</v>
+        <v>-7.388738400000001</v>
       </c>
       <c r="O70">
-        <v>-1.685631200000001</v>
+        <v>-1.8471846</v>
       </c>
       <c r="P70">
-        <v>-5.056893600000004</v>
+        <v>-5.541553800000001</v>
       </c>
       <c r="Q70">
-        <v>-2.756893600000003</v>
+        <v>-3.2415538</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.3907362801568863</v>
+        <v>0.4018632569361407</v>
       </c>
       <c r="T70">
-        <v>3.335797457843465</v>
+        <v>3.443403827451319</v>
       </c>
       <c r="U70">
         <v>0.1468</v>
       </c>
       <c r="V70">
-        <v>0.2116400921960679</v>
+        <v>0.2085728444830814</v>
       </c>
       <c r="W70">
-        <v>0.1157312344656172</v>
+        <v>0.1161815064298837</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7047,7 +7047,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.8465603687842715</v>
+        <v>0.8342913779323256</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7055,22 +7055,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2047428490868233</v>
+        <v>0.2057528490868233</v>
       </c>
       <c r="C71">
-        <v>63.67219799692054</v>
+        <v>57.16492571262313</v>
       </c>
       <c r="D71">
-        <v>333.4101979969205</v>
+        <v>331.3049257126232</v>
       </c>
       <c r="E71">
-        <v>248.938</v>
+        <v>253.34</v>
       </c>
       <c r="F71">
-        <v>303.738</v>
+        <v>308.14</v>
       </c>
       <c r="G71">
         <v>34</v>
@@ -7091,37 +7091,37 @@
         <v>37.2</v>
       </c>
       <c r="M71">
-        <v>44.5887384</v>
+        <v>45.23495200000001</v>
       </c>
       <c r="N71">
-        <v>-7.388738400000001</v>
+        <v>-8.034952000000011</v>
       </c>
       <c r="O71">
-        <v>-1.8471846</v>
+        <v>-2.008738000000003</v>
       </c>
       <c r="P71">
-        <v>-5.541553800000001</v>
+        <v>-6.026214000000008</v>
       </c>
       <c r="Q71">
-        <v>-3.2415538</v>
+        <v>-3.726214000000008</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.4018632569361407</v>
+        <v>0.4137320321673454</v>
       </c>
       <c r="T71">
-        <v>3.443403827451319</v>
+        <v>3.55818395503303</v>
       </c>
       <c r="U71">
         <v>0.1468</v>
       </c>
       <c r="V71">
-        <v>0.2085728444830814</v>
+        <v>0.2055932324190373</v>
       </c>
       <c r="W71">
-        <v>0.1161815064298837</v>
+        <v>0.1166189134808853</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7129,7 +7129,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.8342913779323256</v>
+        <v>0.8223729296761494</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7137,22 +7137,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2057528490868233</v>
+        <v>0.2067628490868234</v>
       </c>
       <c r="C72">
-        <v>57.16492571262313</v>
+        <v>50.68407350002803</v>
       </c>
       <c r="D72">
-        <v>331.3049257126232</v>
+        <v>329.2260735000281</v>
       </c>
       <c r="E72">
-        <v>253.34</v>
+        <v>257.742</v>
       </c>
       <c r="F72">
-        <v>308.14</v>
+        <v>312.542</v>
       </c>
       <c r="G72">
         <v>34</v>
@@ -7173,37 +7173,37 @@
         <v>37.2</v>
       </c>
       <c r="M72">
-        <v>45.23495200000001</v>
+        <v>45.88116560000001</v>
       </c>
       <c r="N72">
-        <v>-8.034952000000011</v>
+        <v>-8.681165600000007</v>
       </c>
       <c r="O72">
-        <v>-2.008738000000003</v>
+        <v>-2.170291400000002</v>
       </c>
       <c r="P72">
-        <v>-6.026214000000008</v>
+        <v>-6.510874200000005</v>
       </c>
       <c r="Q72">
-        <v>-3.726214000000008</v>
+        <v>-4.210874200000005</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.4137320321673454</v>
+        <v>0.4264193436213918</v>
       </c>
       <c r="T72">
-        <v>3.55818395503303</v>
+        <v>3.680879953482445</v>
       </c>
       <c r="U72">
         <v>0.1468</v>
       </c>
       <c r="V72">
-        <v>0.2055932324190373</v>
+        <v>0.2026975530891918</v>
       </c>
       <c r="W72">
-        <v>0.1166189134808853</v>
+        <v>0.1170439992065067</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7211,7 +7211,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.8223729296761494</v>
+        <v>0.8107902123567671</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7219,22 +7219,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2067628490868234</v>
+        <v>0.2516429462929614</v>
       </c>
       <c r="C73">
-        <v>50.68407350002809</v>
+        <v>-25.49934261149235</v>
       </c>
       <c r="D73">
-        <v>329.2260735000281</v>
+        <v>257.4446573885076</v>
       </c>
       <c r="E73">
-        <v>257.742</v>
+        <v>262.1439999999999</v>
       </c>
       <c r="F73">
-        <v>312.542</v>
+        <v>316.944</v>
       </c>
       <c r="G73">
         <v>34</v>
@@ -7255,45 +7255,45 @@
         <v>37.2</v>
       </c>
       <c r="M73">
-        <v>45.8811656</v>
+        <v>63.6423552</v>
       </c>
       <c r="N73">
-        <v>-8.6811656</v>
+        <v>-26.44235519999999</v>
       </c>
       <c r="O73">
-        <v>-2.1702914</v>
+        <v>-6.610588799999999</v>
       </c>
       <c r="P73">
-        <v>-6.5108742</v>
+        <v>-19.8317664</v>
       </c>
       <c r="Q73">
-        <v>-4.210874199999999</v>
+        <v>-17.5317664</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.4264193436213917</v>
+        <v>0.4578346673440774</v>
       </c>
       <c r="T73">
-        <v>3.680879953482445</v>
+        <v>3.984690144059674</v>
       </c>
       <c r="U73">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V73">
-        <v>0.2026975530891918</v>
+        <v>0.1461290986289584</v>
       </c>
       <c r="W73">
-        <v>0.1170439992065067</v>
+        <v>0.1714572769953052</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y73">
-        <v>0.8107902123567672</v>
+        <v>0.5845163945158334</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7301,22 +7301,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2516429462929614</v>
+        <v>0.2531929462929614</v>
       </c>
       <c r="C74">
-        <v>-25.49934261149235</v>
+        <v>-31.82541585547102</v>
       </c>
       <c r="D74">
-        <v>257.4446573885076</v>
+        <v>255.520584144529</v>
       </c>
       <c r="E74">
-        <v>262.1439999999999</v>
+        <v>266.546</v>
       </c>
       <c r="F74">
-        <v>316.944</v>
+        <v>321.346</v>
       </c>
       <c r="G74">
         <v>34</v>
@@ -7337,37 +7337,37 @@
         <v>37.2</v>
       </c>
       <c r="M74">
-        <v>63.6423552</v>
+        <v>64.52627680000001</v>
       </c>
       <c r="N74">
-        <v>-26.44235519999999</v>
+        <v>-27.3262768</v>
       </c>
       <c r="O74">
-        <v>-6.610588799999999</v>
+        <v>-6.831569200000001</v>
       </c>
       <c r="P74">
-        <v>-19.8317664</v>
+        <v>-20.4947076</v>
       </c>
       <c r="Q74">
-        <v>-17.5317664</v>
+        <v>-18.1947076</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.4578346673440774</v>
+        <v>0.4730952105790431</v>
       </c>
       <c r="T74">
-        <v>3.984690144059674</v>
+        <v>4.132271260506328</v>
       </c>
       <c r="U74">
         <v>0.2008</v>
       </c>
       <c r="V74">
-        <v>0.1461290986289584</v>
+        <v>0.1441273301545891</v>
       </c>
       <c r="W74">
-        <v>0.1714572769953052</v>
+        <v>0.1718592321049585</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7375,7 +7375,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.5845163945158334</v>
+        <v>0.5765093206183562</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7383,22 +7383,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2531929462929614</v>
+        <v>0.2547429462929613</v>
       </c>
       <c r="C75">
-        <v>-31.82541585547102</v>
+        <v>-38.12294242121919</v>
       </c>
       <c r="D75">
-        <v>255.520584144529</v>
+        <v>253.6250575787808</v>
       </c>
       <c r="E75">
-        <v>266.546</v>
+        <v>270.948</v>
       </c>
       <c r="F75">
-        <v>321.346</v>
+        <v>325.748</v>
       </c>
       <c r="G75">
         <v>34</v>
@@ -7419,37 +7419,37 @@
         <v>37.2</v>
       </c>
       <c r="M75">
-        <v>64.52627680000001</v>
+        <v>65.4101984</v>
       </c>
       <c r="N75">
-        <v>-27.3262768</v>
+        <v>-28.2101984</v>
       </c>
       <c r="O75">
-        <v>-6.831569200000001</v>
+        <v>-7.052549599999999</v>
       </c>
       <c r="P75">
-        <v>-20.4947076</v>
+        <v>-21.1576488</v>
       </c>
       <c r="Q75">
-        <v>-18.1947076</v>
+        <v>-18.8576488</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.4730952105790431</v>
+        <v>0.4895296417551602</v>
       </c>
       <c r="T75">
-        <v>4.132271260506328</v>
+        <v>4.291204770525803</v>
       </c>
       <c r="U75">
         <v>0.2008</v>
       </c>
       <c r="V75">
-        <v>0.1441273301545891</v>
+        <v>0.1421796635308784</v>
       </c>
       <c r="W75">
-        <v>0.1718592321049585</v>
+        <v>0.1722503235629996</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7457,7 +7457,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.5765093206183562</v>
+        <v>0.5687186541235136</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7465,22 +7465,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2547429462929613</v>
+        <v>0.2562929462929614</v>
       </c>
       <c r="C76">
-        <v>-38.12294242121919</v>
+        <v>-44.39255293344974</v>
       </c>
       <c r="D76">
-        <v>253.6250575787808</v>
+        <v>251.7574470665502</v>
       </c>
       <c r="E76">
-        <v>270.948</v>
+        <v>275.35</v>
       </c>
       <c r="F76">
-        <v>325.748</v>
+        <v>330.15</v>
       </c>
       <c r="G76">
         <v>34</v>
@@ -7501,37 +7501,37 @@
         <v>37.2</v>
       </c>
       <c r="M76">
-        <v>65.4101984</v>
+        <v>66.29411999999999</v>
       </c>
       <c r="N76">
-        <v>-28.2101984</v>
+        <v>-29.09411999999999</v>
       </c>
       <c r="O76">
-        <v>-7.052549599999999</v>
+        <v>-7.273529999999997</v>
       </c>
       <c r="P76">
-        <v>-21.1576488</v>
+        <v>-21.82058999999999</v>
       </c>
       <c r="Q76">
-        <v>-18.8576488</v>
+        <v>-19.52058999999999</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.4895296417551602</v>
+        <v>0.5072788274253667</v>
       </c>
       <c r="T76">
-        <v>4.291204770525803</v>
+        <v>4.462852961346835</v>
       </c>
       <c r="U76">
         <v>0.2008</v>
       </c>
       <c r="V76">
-        <v>0.1421796635308784</v>
+        <v>0.1402839346838</v>
       </c>
       <c r="W76">
-        <v>0.1722503235629996</v>
+        <v>0.1726309859154929</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7539,7 +7539,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.5687186541235136</v>
+        <v>0.5611357387352002</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7547,22 +7547,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2562929462929614</v>
+        <v>0.2578429462929613</v>
       </c>
       <c r="C77">
-        <v>-44.39255293344974</v>
+        <v>-50.63485957781222</v>
       </c>
       <c r="D77">
-        <v>251.7574470665502</v>
+        <v>249.9171404221878</v>
       </c>
       <c r="E77">
-        <v>275.35</v>
+        <v>279.752</v>
       </c>
       <c r="F77">
-        <v>330.15</v>
+        <v>334.552</v>
       </c>
       <c r="G77">
         <v>34</v>
@@ -7583,37 +7583,37 @@
         <v>37.2</v>
       </c>
       <c r="M77">
-        <v>66.29411999999999</v>
+        <v>67.1780416</v>
       </c>
       <c r="N77">
-        <v>-29.09411999999999</v>
+        <v>-29.9780416</v>
       </c>
       <c r="O77">
-        <v>-7.273529999999997</v>
+        <v>-7.494510399999999</v>
       </c>
       <c r="P77">
-        <v>-21.82058999999999</v>
+        <v>-22.4835312</v>
       </c>
       <c r="Q77">
-        <v>-19.52058999999999</v>
+        <v>-20.1835312</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.5072788274253667</v>
+        <v>0.5265071119014236</v>
       </c>
       <c r="T77">
-        <v>4.462852961346835</v>
+        <v>4.64880516806962</v>
       </c>
       <c r="U77">
         <v>0.2008</v>
       </c>
       <c r="V77">
-        <v>0.1402839346838</v>
+        <v>0.1384380934379605</v>
       </c>
       <c r="W77">
-        <v>0.1726309859154929</v>
+        <v>0.1730016308376575</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7621,7 +7621,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.5611357387352002</v>
+        <v>0.5537523737518422</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7629,22 +7629,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2578429462929613</v>
+        <v>0.2593929462929614</v>
       </c>
       <c r="C78">
-        <v>-50.63485957781222</v>
+        <v>-56.85045676993627</v>
       </c>
       <c r="D78">
-        <v>249.9171404221878</v>
+        <v>248.1035432300637</v>
       </c>
       <c r="E78">
-        <v>279.752</v>
+        <v>284.154</v>
       </c>
       <c r="F78">
-        <v>334.552</v>
+        <v>338.954</v>
       </c>
       <c r="G78">
         <v>34</v>
@@ -7665,37 +7665,37 @@
         <v>37.2</v>
       </c>
       <c r="M78">
-        <v>67.1780416</v>
+        <v>68.06196320000001</v>
       </c>
       <c r="N78">
-        <v>-29.9780416</v>
+        <v>-30.86196320000001</v>
       </c>
       <c r="O78">
-        <v>-7.494510399999999</v>
+        <v>-7.715490800000001</v>
       </c>
       <c r="P78">
-        <v>-22.4835312</v>
+        <v>-23.1464724</v>
       </c>
       <c r="Q78">
-        <v>-20.1835312</v>
+        <v>-20.8464724</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.5265071119014236</v>
+        <v>0.547407421114529</v>
       </c>
       <c r="T78">
-        <v>4.64880516806962</v>
+        <v>4.850927131898734</v>
       </c>
       <c r="U78">
         <v>0.2008</v>
       </c>
       <c r="V78">
-        <v>0.1384380934379605</v>
+        <v>0.1366401961205844</v>
       </c>
       <c r="W78">
-        <v>0.1730016308376575</v>
+        <v>0.1733626486189866</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7703,7 +7703,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.5537523737518422</v>
+        <v>0.5465607844823377</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7711,22 +7711,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2593929462929614</v>
+        <v>0.2609429462929613</v>
       </c>
       <c r="C79">
-        <v>-56.85045676993627</v>
+        <v>-63.039921795552</v>
       </c>
       <c r="D79">
-        <v>248.1035432300637</v>
+        <v>246.316078204448</v>
       </c>
       <c r="E79">
-        <v>284.154</v>
+        <v>288.556</v>
       </c>
       <c r="F79">
-        <v>338.954</v>
+        <v>343.356</v>
       </c>
       <c r="G79">
         <v>34</v>
@@ -7747,37 +7747,37 @@
         <v>37.2</v>
       </c>
       <c r="M79">
-        <v>68.06196320000001</v>
+        <v>68.9458848</v>
       </c>
       <c r="N79">
-        <v>-30.86196320000001</v>
+        <v>-31.7458848</v>
       </c>
       <c r="O79">
-        <v>-7.715490800000001</v>
+        <v>-7.9364712</v>
       </c>
       <c r="P79">
-        <v>-23.1464724</v>
+        <v>-23.8094136</v>
       </c>
       <c r="Q79">
-        <v>-20.8464724</v>
+        <v>-21.5094136</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.547407421114529</v>
+        <v>0.5702077584379166</v>
       </c>
       <c r="T79">
-        <v>4.850927131898734</v>
+        <v>5.071423819712312</v>
       </c>
       <c r="U79">
         <v>0.2008</v>
       </c>
       <c r="V79">
-        <v>0.1366401961205844</v>
+        <v>0.1348883987344231</v>
       </c>
       <c r="W79">
-        <v>0.1733626486189866</v>
+        <v>0.1737144095341278</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7785,7 +7785,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.5465607844823377</v>
+        <v>0.5395535949376924</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7793,22 +7793,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2609429462929613</v>
+        <v>0.2624929462929614</v>
       </c>
       <c r="C80">
-        <v>-63.039921795552</v>
+        <v>-69.20381542314027</v>
       </c>
       <c r="D80">
-        <v>246.316078204448</v>
+        <v>244.5541845768597</v>
       </c>
       <c r="E80">
-        <v>288.556</v>
+        <v>292.958</v>
       </c>
       <c r="F80">
-        <v>343.356</v>
+        <v>347.758</v>
       </c>
       <c r="G80">
         <v>34</v>
@@ -7829,37 +7829,37 @@
         <v>37.2</v>
       </c>
       <c r="M80">
-        <v>68.9458848</v>
+        <v>69.8298064</v>
       </c>
       <c r="N80">
-        <v>-31.7458848</v>
+        <v>-32.62980639999999</v>
       </c>
       <c r="O80">
-        <v>-7.9364712</v>
+        <v>-8.157451599999998</v>
       </c>
       <c r="P80">
-        <v>-23.8094136</v>
+        <v>-24.47235479999999</v>
       </c>
       <c r="Q80">
-        <v>-21.5094136</v>
+        <v>-22.17235479999999</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.5702077584379166</v>
+        <v>0.5951795564587699</v>
       </c>
       <c r="T80">
-        <v>5.071423819712312</v>
+        <v>5.312920192079567</v>
       </c>
       <c r="U80">
         <v>0.2008</v>
       </c>
       <c r="V80">
-        <v>0.1348883987344231</v>
+        <v>0.1331809506491772</v>
       </c>
       <c r="W80">
-        <v>0.1737144095341278</v>
+        <v>0.1740572651096452</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7867,7 +7867,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.5395535949376924</v>
+        <v>0.5327238025967089</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7875,22 +7875,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2624929462929614</v>
+        <v>0.2640429462929614</v>
       </c>
       <c r="C81">
-        <v>-69.20381542314027</v>
+        <v>-75.34268249047403</v>
       </c>
       <c r="D81">
-        <v>244.5541845768597</v>
+        <v>242.817317509526</v>
       </c>
       <c r="E81">
-        <v>292.958</v>
+        <v>297.36</v>
       </c>
       <c r="F81">
-        <v>347.758</v>
+        <v>352.16</v>
       </c>
       <c r="G81">
         <v>34</v>
@@ -7911,37 +7911,37 @@
         <v>37.2</v>
       </c>
       <c r="M81">
-        <v>69.8298064</v>
+        <v>70.713728</v>
       </c>
       <c r="N81">
-        <v>-32.62980639999999</v>
+        <v>-33.513728</v>
       </c>
       <c r="O81">
-        <v>-8.157451599999998</v>
+        <v>-8.378432</v>
       </c>
       <c r="P81">
-        <v>-24.47235479999999</v>
+        <v>-25.135296</v>
       </c>
       <c r="Q81">
-        <v>-22.17235479999999</v>
+        <v>-22.835296</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.5951795564587699</v>
+        <v>0.6226485342817084</v>
       </c>
       <c r="T81">
-        <v>5.312920192079567</v>
+        <v>5.578566201683545</v>
       </c>
       <c r="U81">
         <v>0.2008</v>
       </c>
       <c r="V81">
-        <v>0.1331809506491772</v>
+        <v>0.1315161887660625</v>
       </c>
       <c r="W81">
-        <v>0.1740572651096452</v>
+        <v>0.1743915492957747</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7949,7 +7949,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.5327238025967089</v>
+        <v>0.5260647550642501</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7957,22 +7957,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2640429462929614</v>
+        <v>0.2655929462929614</v>
       </c>
       <c r="C82">
-        <v>-75.34268249047403</v>
+        <v>-81.4570524663427</v>
       </c>
       <c r="D82">
-        <v>242.817317509526</v>
+        <v>241.1049475336573</v>
       </c>
       <c r="E82">
-        <v>297.36</v>
+        <v>301.762</v>
       </c>
       <c r="F82">
-        <v>352.16</v>
+        <v>356.562</v>
       </c>
       <c r="G82">
         <v>34</v>
@@ -7993,37 +7993,37 @@
         <v>37.2</v>
       </c>
       <c r="M82">
-        <v>70.713728</v>
+        <v>71.59764960000001</v>
       </c>
       <c r="N82">
-        <v>-33.513728</v>
+        <v>-34.39764960000001</v>
       </c>
       <c r="O82">
-        <v>-8.378432</v>
+        <v>-8.599412400000002</v>
       </c>
       <c r="P82">
-        <v>-25.135296</v>
+        <v>-25.79823720000001</v>
       </c>
       <c r="Q82">
-        <v>-22.835296</v>
+        <v>-23.49823720000001</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.6226485342817084</v>
+        <v>0.6530089834544299</v>
       </c>
       <c r="T82">
-        <v>5.578566201683545</v>
+        <v>5.872174949140574</v>
       </c>
       <c r="U82">
         <v>0.2008</v>
       </c>
       <c r="V82">
-        <v>0.1315161887660625</v>
+        <v>0.1298925321146296</v>
       </c>
       <c r="W82">
-        <v>0.1743915492957747</v>
+        <v>0.1747175795513824</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8031,7 +8031,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.5260647550642501</v>
+        <v>0.5195701284585186</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8039,22 +8039,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2655929462929614</v>
+        <v>0.2671429462929614</v>
       </c>
       <c r="C83">
-        <v>-81.4570524663427</v>
+        <v>-87.54743998867428</v>
       </c>
       <c r="D83">
-        <v>241.1049475336573</v>
+        <v>239.4165600113257</v>
       </c>
       <c r="E83">
-        <v>301.762</v>
+        <v>306.164</v>
       </c>
       <c r="F83">
-        <v>356.562</v>
+        <v>360.964</v>
       </c>
       <c r="G83">
         <v>34</v>
@@ -8075,37 +8075,37 @@
         <v>37.2</v>
       </c>
       <c r="M83">
-        <v>71.59764960000001</v>
+        <v>72.4815712</v>
       </c>
       <c r="N83">
-        <v>-34.39764960000001</v>
+        <v>-35.2815712</v>
       </c>
       <c r="O83">
-        <v>-8.599412400000002</v>
+        <v>-8.8203928</v>
       </c>
       <c r="P83">
-        <v>-25.79823720000001</v>
+        <v>-26.4611784</v>
       </c>
       <c r="Q83">
-        <v>-23.49823720000001</v>
+        <v>-24.1611784</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.6530089834544299</v>
+        <v>0.6867428158685649</v>
       </c>
       <c r="T83">
-        <v>5.872174949140574</v>
+        <v>6.198406890759494</v>
       </c>
       <c r="U83">
         <v>0.2008</v>
       </c>
       <c r="V83">
-        <v>0.1298925321146296</v>
+        <v>0.128308476844939</v>
       </c>
       <c r="W83">
-        <v>0.1747175795513824</v>
+        <v>0.1750356578495362</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8113,7 +8113,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.5195701284585186</v>
+        <v>0.5132339073797562</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8121,22 +8121,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2671429462929614</v>
+        <v>0.2686929462929614</v>
       </c>
       <c r="C84">
-        <v>-87.54743998867428</v>
+        <v>-93.61434538020609</v>
       </c>
       <c r="D84">
-        <v>239.4165600113257</v>
+        <v>237.751654619794</v>
       </c>
       <c r="E84">
-        <v>306.164</v>
+        <v>310.566</v>
       </c>
       <c r="F84">
-        <v>360.964</v>
+        <v>365.366</v>
       </c>
       <c r="G84">
         <v>34</v>
@@ -8157,37 +8157,37 @@
         <v>37.2</v>
       </c>
       <c r="M84">
-        <v>72.4815712</v>
+        <v>73.36549280000001</v>
       </c>
       <c r="N84">
-        <v>-35.2815712</v>
+        <v>-36.16549280000001</v>
       </c>
       <c r="O84">
-        <v>-8.8203928</v>
+        <v>-9.041373200000002</v>
       </c>
       <c r="P84">
-        <v>-26.4611784</v>
+        <v>-27.12411960000001</v>
       </c>
       <c r="Q84">
-        <v>-24.1611784</v>
+        <v>-24.82411960000001</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.6867428158685649</v>
+        <v>0.7244453344490689</v>
       </c>
       <c r="T84">
-        <v>6.198406890759494</v>
+        <v>6.563019060804172</v>
       </c>
       <c r="U84">
         <v>0.2008</v>
       </c>
       <c r="V84">
-        <v>0.128308476844939</v>
+        <v>0.126762591581747</v>
       </c>
       <c r="W84">
-        <v>0.1750356578495362</v>
+        <v>0.1753460716103852</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8195,7 +8195,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.5132339073797562</v>
+        <v>0.507050366326988</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8203,22 +8203,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2686929462929614</v>
+        <v>0.2702429462929614</v>
       </c>
       <c r="C85">
-        <v>-93.61434538020609</v>
+        <v>-99.65825514278635</v>
       </c>
       <c r="D85">
-        <v>237.751654619794</v>
+        <v>236.1097448572137</v>
       </c>
       <c r="E85">
-        <v>310.566</v>
+        <v>314.968</v>
       </c>
       <c r="F85">
-        <v>365.366</v>
+        <v>369.768</v>
       </c>
       <c r="G85">
         <v>34</v>
@@ -8239,37 +8239,37 @@
         <v>37.2</v>
       </c>
       <c r="M85">
-        <v>73.36549280000001</v>
+        <v>74.24941440000001</v>
       </c>
       <c r="N85">
-        <v>-36.16549280000001</v>
+        <v>-37.0494144</v>
       </c>
       <c r="O85">
-        <v>-9.041373200000002</v>
+        <v>-9.262353600000001</v>
       </c>
       <c r="P85">
-        <v>-27.12411960000001</v>
+        <v>-27.7870608</v>
       </c>
       <c r="Q85">
-        <v>-24.82411960000001</v>
+        <v>-25.4870608</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.7244453344490689</v>
+        <v>0.7668606678521358</v>
       </c>
       <c r="T85">
-        <v>6.563019060804172</v>
+        <v>6.973207752104434</v>
       </c>
       <c r="U85">
         <v>0.2008</v>
       </c>
       <c r="V85">
-        <v>0.126762591581747</v>
+        <v>0.1252535131105357</v>
       </c>
       <c r="W85">
-        <v>0.1753460716103852</v>
+        <v>0.1756490945674044</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8277,7 +8277,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.507050366326988</v>
+        <v>0.5010140524421429</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8285,22 +8285,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2702429462929614</v>
+        <v>0.3035565107893282</v>
       </c>
       <c r="C86">
-        <v>-99.65825514278623</v>
+        <v>-134.5760981352076</v>
       </c>
       <c r="D86">
-        <v>236.1097448572137</v>
+        <v>205.5939018647924</v>
       </c>
       <c r="E86">
-        <v>314.968</v>
+        <v>319.3699999999999</v>
       </c>
       <c r="F86">
-        <v>369.768</v>
+        <v>374.17</v>
       </c>
       <c r="G86">
         <v>34</v>
@@ -8321,45 +8321,45 @@
         <v>37.2</v>
       </c>
       <c r="M86">
-        <v>74.24941439999999</v>
+        <v>88.22928599999999</v>
       </c>
       <c r="N86">
-        <v>-37.04941439999999</v>
+        <v>-51.02928599999998</v>
       </c>
       <c r="O86">
-        <v>-9.262353599999997</v>
+        <v>-12.7573215</v>
       </c>
       <c r="P86">
-        <v>-27.78706079999999</v>
+        <v>-38.27196449999999</v>
       </c>
       <c r="Q86">
-        <v>-25.48706079999999</v>
+        <v>-35.97196449999998</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.7668606678521351</v>
+        <v>0.8283551423513895</v>
       </c>
       <c r="T86">
-        <v>6.973207752104428</v>
+        <v>7.567906319656476</v>
       </c>
       <c r="U86">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.1252535131105358</v>
+        <v>0.1054071773855226</v>
       </c>
       <c r="W86">
-        <v>0.1756490945674044</v>
+        <v>0.2109449875724938</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y86">
-        <v>0.5010140524421429</v>
+        <v>0.4216287095420902</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8367,22 +8367,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.3035565107893282</v>
+        <v>0.3054565107893281</v>
       </c>
       <c r="C87">
-        <v>-134.5760981352076</v>
+        <v>-140.4825025976862</v>
       </c>
       <c r="D87">
-        <v>205.5939018647924</v>
+        <v>204.0894974023138</v>
       </c>
       <c r="E87">
-        <v>319.3699999999999</v>
+        <v>323.772</v>
       </c>
       <c r="F87">
-        <v>374.17</v>
+        <v>378.572</v>
       </c>
       <c r="G87">
         <v>34</v>
@@ -8403,37 +8403,37 @@
         <v>37.2</v>
       </c>
       <c r="M87">
-        <v>88.22928599999999</v>
+        <v>89.2672776</v>
       </c>
       <c r="N87">
-        <v>-51.02928599999998</v>
+        <v>-52.0672776</v>
       </c>
       <c r="O87">
-        <v>-12.7573215</v>
+        <v>-13.0168194</v>
       </c>
       <c r="P87">
-        <v>-38.27196449999999</v>
+        <v>-39.05045819999999</v>
       </c>
       <c r="Q87">
-        <v>-35.97196449999998</v>
+        <v>-36.7504582</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.8283551423513895</v>
+        <v>0.8842519382336316</v>
       </c>
       <c r="T87">
-        <v>7.567906319656476</v>
+        <v>8.108471056774796</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.1054071773855226</v>
+        <v>0.1041815125322025</v>
       </c>
       <c r="W87">
-        <v>0.2109449875724938</v>
+        <v>0.2112339993449067</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8441,7 +8441,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.4216287095420902</v>
+        <v>0.41672605012881</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8449,22 +8449,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.3054565107893281</v>
+        <v>0.3073565107893281</v>
       </c>
       <c r="C88">
-        <v>-140.4825025976862</v>
+        <v>-146.3670504566334</v>
       </c>
       <c r="D88">
-        <v>204.0894974023138</v>
+        <v>202.6069495433666</v>
       </c>
       <c r="E88">
-        <v>323.772</v>
+        <v>328.174</v>
       </c>
       <c r="F88">
-        <v>378.572</v>
+        <v>382.974</v>
       </c>
       <c r="G88">
         <v>34</v>
@@ -8485,37 +8485,37 @@
         <v>37.2</v>
       </c>
       <c r="M88">
-        <v>89.2672776</v>
+        <v>90.3052692</v>
       </c>
       <c r="N88">
-        <v>-52.0672776</v>
+        <v>-53.1052692</v>
       </c>
       <c r="O88">
-        <v>-13.0168194</v>
+        <v>-13.2763173</v>
       </c>
       <c r="P88">
-        <v>-39.05045819999999</v>
+        <v>-39.82895189999999</v>
       </c>
       <c r="Q88">
-        <v>-36.7504582</v>
+        <v>-37.5289519</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.8842519382336316</v>
+        <v>0.9487482411746803</v>
       </c>
       <c r="T88">
-        <v>8.108471056774796</v>
+        <v>8.732199599603627</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.1041815125322025</v>
+        <v>0.1029840238824071</v>
       </c>
       <c r="W88">
-        <v>0.2112339993449067</v>
+        <v>0.2115163671685284</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8523,7 +8523,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.41672605012881</v>
+        <v>0.4119360955296283</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8531,22 +8531,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.3073565107893281</v>
+        <v>0.3092565107893281</v>
       </c>
       <c r="C89">
-        <v>-146.3670504566334</v>
+        <v>-152.230214589488</v>
       </c>
       <c r="D89">
-        <v>202.6069495433666</v>
+        <v>201.145785410512</v>
       </c>
       <c r="E89">
-        <v>328.174</v>
+        <v>332.576</v>
       </c>
       <c r="F89">
-        <v>382.974</v>
+        <v>387.376</v>
       </c>
       <c r="G89">
         <v>34</v>
@@ -8567,37 +8567,37 @@
         <v>37.2</v>
       </c>
       <c r="M89">
-        <v>90.3052692</v>
+        <v>91.3432608</v>
       </c>
       <c r="N89">
-        <v>-53.1052692</v>
+        <v>-54.14326079999999</v>
       </c>
       <c r="O89">
-        <v>-13.2763173</v>
+        <v>-13.5358152</v>
       </c>
       <c r="P89">
-        <v>-39.82895189999999</v>
+        <v>-40.60744559999999</v>
       </c>
       <c r="Q89">
-        <v>-37.5289519</v>
+        <v>-38.30744559999999</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.9487482411746803</v>
+        <v>1.023993927939237</v>
       </c>
       <c r="T89">
-        <v>8.732199599603627</v>
+        <v>9.459882899570598</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.1029840238824071</v>
+        <v>0.1018137508837434</v>
       </c>
       <c r="W89">
-        <v>0.2115163671685284</v>
+        <v>0.2117923175416133</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8605,7 +8605,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.4119360955296283</v>
+        <v>0.4072550035349735</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8613,22 +8613,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.3092565107893281</v>
+        <v>0.3111565107893282</v>
       </c>
       <c r="C90">
-        <v>-152.230214589488</v>
+        <v>-158.0724543301417</v>
       </c>
       <c r="D90">
-        <v>201.145785410512</v>
+        <v>199.7055456698583</v>
       </c>
       <c r="E90">
-        <v>332.576</v>
+        <v>336.978</v>
       </c>
       <c r="F90">
-        <v>387.376</v>
+        <v>391.778</v>
       </c>
       <c r="G90">
         <v>34</v>
@@ -8649,37 +8649,37 @@
         <v>37.2</v>
       </c>
       <c r="M90">
-        <v>91.3432608</v>
+        <v>92.38125240000001</v>
       </c>
       <c r="N90">
-        <v>-54.14326079999999</v>
+        <v>-55.18125240000001</v>
       </c>
       <c r="O90">
-        <v>-13.5358152</v>
+        <v>-13.7953131</v>
       </c>
       <c r="P90">
-        <v>-40.60744559999999</v>
+        <v>-41.3859393</v>
       </c>
       <c r="Q90">
-        <v>-38.30744559999999</v>
+        <v>-39.08593930000001</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>1.023993927939237</v>
+        <v>1.112920648660986</v>
       </c>
       <c r="T90">
-        <v>9.459882899570598</v>
+        <v>10.31987225407702</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.1018137508837434</v>
+        <v>0.1006697761547125</v>
       </c>
       <c r="W90">
-        <v>0.2117923175416133</v>
+        <v>0.2120620667827188</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8687,7 +8687,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.4072550035349735</v>
+        <v>0.4026791046188501</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8695,22 +8695,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.3111565107893282</v>
+        <v>0.3130565107893282</v>
       </c>
       <c r="C91">
-        <v>-158.0724543301417</v>
+        <v>-163.8942159503622</v>
       </c>
       <c r="D91">
-        <v>199.7055456698583</v>
+        <v>198.2857840496378</v>
       </c>
       <c r="E91">
-        <v>336.978</v>
+        <v>341.38</v>
       </c>
       <c r="F91">
-        <v>391.778</v>
+        <v>396.18</v>
       </c>
       <c r="G91">
         <v>34</v>
@@ -8731,37 +8731,37 @@
         <v>37.2</v>
       </c>
       <c r="M91">
-        <v>92.38125240000001</v>
+        <v>93.41924400000001</v>
       </c>
       <c r="N91">
-        <v>-55.18125240000001</v>
+        <v>-56.219244</v>
       </c>
       <c r="O91">
-        <v>-13.7953131</v>
+        <v>-14.054811</v>
       </c>
       <c r="P91">
-        <v>-41.3859393</v>
+        <v>-42.164433</v>
       </c>
       <c r="Q91">
-        <v>-39.08593930000001</v>
+        <v>-39.86443300000001</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>1.112920648660986</v>
+        <v>1.219632713527085</v>
       </c>
       <c r="T91">
-        <v>10.31987225407702</v>
+        <v>11.35185947948472</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.1006697761547125</v>
+        <v>0.09955122308632684</v>
       </c>
       <c r="W91">
-        <v>0.2120620667827188</v>
+        <v>0.2123258215962441</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8769,7 +8769,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.4026791046188501</v>
+        <v>0.3982048923453073</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8777,22 +8777,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.3130565107893282</v>
+        <v>0.3149565107893282</v>
       </c>
       <c r="C92">
-        <v>-163.8942159503622</v>
+        <v>-169.6959331208273</v>
       </c>
       <c r="D92">
-        <v>198.2857840496378</v>
+        <v>196.8860668791727</v>
       </c>
       <c r="E92">
-        <v>341.38</v>
+        <v>345.782</v>
       </c>
       <c r="F92">
-        <v>396.18</v>
+        <v>400.582</v>
       </c>
       <c r="G92">
         <v>34</v>
@@ -8813,37 +8813,37 @@
         <v>37.2</v>
       </c>
       <c r="M92">
-        <v>93.41924400000001</v>
+        <v>94.4572356</v>
       </c>
       <c r="N92">
-        <v>-56.219244</v>
+        <v>-57.2572356</v>
       </c>
       <c r="O92">
-        <v>-14.054811</v>
+        <v>-14.3143089</v>
       </c>
       <c r="P92">
-        <v>-42.164433</v>
+        <v>-42.9429267</v>
       </c>
       <c r="Q92">
-        <v>-39.86443300000001</v>
+        <v>-40.6429267</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>1.219632713527085</v>
+        <v>1.35005857058565</v>
       </c>
       <c r="T92">
-        <v>11.35185947948472</v>
+        <v>12.61317719942747</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.09955122308632684</v>
+        <v>0.09845725360186171</v>
       </c>
       <c r="W92">
-        <v>0.2123258215962441</v>
+        <v>0.212583779600681</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8851,7 +8851,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3982048923453073</v>
+        <v>0.3938290144074469</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8859,22 +8859,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.3149565107893282</v>
+        <v>0.3168565107893282</v>
       </c>
       <c r="C93">
-        <v>-169.6959331208273</v>
+        <v>-175.4780273527684</v>
       </c>
       <c r="D93">
-        <v>196.8860668791727</v>
+        <v>195.5059726472316</v>
       </c>
       <c r="E93">
-        <v>345.782</v>
+        <v>350.184</v>
       </c>
       <c r="F93">
-        <v>400.582</v>
+        <v>404.984</v>
       </c>
       <c r="G93">
         <v>34</v>
@@ -8895,37 +8895,37 @@
         <v>37.2</v>
       </c>
       <c r="M93">
-        <v>94.4572356</v>
+        <v>95.4952272</v>
       </c>
       <c r="N93">
-        <v>-57.2572356</v>
+        <v>-58.2952272</v>
       </c>
       <c r="O93">
-        <v>-14.3143089</v>
+        <v>-14.5738068</v>
       </c>
       <c r="P93">
-        <v>-42.9429267</v>
+        <v>-43.7214204</v>
       </c>
       <c r="Q93">
-        <v>-40.6429267</v>
+        <v>-41.4214204</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>1.35005857058565</v>
+        <v>1.513090891908856</v>
       </c>
       <c r="T93">
-        <v>12.61317719942747</v>
+        <v>14.1898243493559</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.09845725360186171</v>
+        <v>0.09738706606271104</v>
       </c>
       <c r="W93">
-        <v>0.212583779600681</v>
+        <v>0.2128361298224127</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8933,7 +8933,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3938290144074469</v>
+        <v>0.3895482642508442</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8941,22 +8941,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.3168565107893282</v>
+        <v>0.3187565107893282</v>
       </c>
       <c r="C94">
-        <v>-175.4780273527684</v>
+        <v>-181.2409084211685</v>
       </c>
       <c r="D94">
-        <v>195.5059726472316</v>
+        <v>194.1450915788315</v>
       </c>
       <c r="E94">
-        <v>350.184</v>
+        <v>354.586</v>
       </c>
       <c r="F94">
-        <v>404.984</v>
+        <v>409.386</v>
       </c>
       <c r="G94">
         <v>34</v>
@@ -8977,37 +8977,37 @@
         <v>37.2</v>
       </c>
       <c r="M94">
-        <v>95.4952272</v>
+        <v>96.53321880000001</v>
       </c>
       <c r="N94">
-        <v>-58.2952272</v>
+        <v>-59.33321880000001</v>
       </c>
       <c r="O94">
-        <v>-14.5738068</v>
+        <v>-14.8333047</v>
       </c>
       <c r="P94">
-        <v>-43.7214204</v>
+        <v>-44.49991410000001</v>
       </c>
       <c r="Q94">
-        <v>-41.4214204</v>
+        <v>-42.19991410000002</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>1.513090891908856</v>
+        <v>1.722703876467264</v>
       </c>
       <c r="T94">
-        <v>14.1898243493559</v>
+        <v>16.2169421135496</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.09738706606271104</v>
+        <v>0.09633989330934854</v>
       </c>
       <c r="W94">
-        <v>0.2128361298224127</v>
+        <v>0.2130830531576556</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9015,7 +9015,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3895482642508442</v>
+        <v>0.3853595732373942</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9023,22 +9023,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.3187565107893282</v>
+        <v>0.3206565107893282</v>
       </c>
       <c r="C95">
-        <v>-181.2409084211685</v>
+        <v>-186.9849747704081</v>
       </c>
       <c r="D95">
-        <v>194.1450915788315</v>
+        <v>192.8030252295919</v>
       </c>
       <c r="E95">
-        <v>354.586</v>
+        <v>358.988</v>
       </c>
       <c r="F95">
-        <v>409.386</v>
+        <v>413.788</v>
       </c>
       <c r="G95">
         <v>34</v>
@@ -9059,37 +9059,37 @@
         <v>37.2</v>
       </c>
       <c r="M95">
-        <v>96.53321880000001</v>
+        <v>97.57121040000001</v>
       </c>
       <c r="N95">
-        <v>-59.33321880000001</v>
+        <v>-60.37121040000001</v>
       </c>
       <c r="O95">
-        <v>-14.8333047</v>
+        <v>-15.0928026</v>
       </c>
       <c r="P95">
-        <v>-44.49991410000001</v>
+        <v>-45.27840780000001</v>
       </c>
       <c r="Q95">
-        <v>-42.19991410000002</v>
+        <v>-42.97840780000001</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.722703876467264</v>
+        <v>2.002187855878476</v>
       </c>
       <c r="T95">
-        <v>16.2169421135496</v>
+        <v>18.91976579914121</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.09633989330934854</v>
+        <v>0.0953150008273342</v>
       </c>
       <c r="W95">
-        <v>0.2130830531576556</v>
+        <v>0.2133247228049146</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9097,7 +9097,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3853595732373942</v>
+        <v>0.3812600033093368</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9105,22 +9105,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.3206565107893282</v>
+        <v>0.3225565107893281</v>
       </c>
       <c r="C96">
-        <v>-186.9849747704081</v>
+        <v>-192.7106139032019</v>
       </c>
       <c r="D96">
-        <v>192.8030252295919</v>
+        <v>191.4793860967981</v>
       </c>
       <c r="E96">
-        <v>358.988</v>
+        <v>363.39</v>
       </c>
       <c r="F96">
-        <v>413.788</v>
+        <v>418.19</v>
       </c>
       <c r="G96">
         <v>34</v>
@@ -9141,37 +9141,37 @@
         <v>37.2</v>
       </c>
       <c r="M96">
-        <v>97.57121040000001</v>
+        <v>98.60920200000001</v>
       </c>
       <c r="N96">
-        <v>-60.37121040000001</v>
+        <v>-61.40920200000001</v>
       </c>
       <c r="O96">
-        <v>-15.0928026</v>
+        <v>-15.3523005</v>
       </c>
       <c r="P96">
-        <v>-45.27840780000001</v>
+        <v>-46.05690150000001</v>
       </c>
       <c r="Q96">
-        <v>-42.97840780000001</v>
+        <v>-43.75690150000001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>2.002187855878476</v>
+        <v>2.393465427054172</v>
       </c>
       <c r="T96">
-        <v>18.91976579914121</v>
+        <v>22.70371895896946</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.0953150008273342</v>
+        <v>0.09431168502915174</v>
       </c>
       <c r="W96">
-        <v>0.2133247228049146</v>
+        <v>0.213561304670126</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9179,7 +9179,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3812600033093368</v>
+        <v>0.377246740116607</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9187,22 +9187,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.3225565107893281</v>
+        <v>0.3244565107893281</v>
       </c>
       <c r="C97">
-        <v>-192.7106139032019</v>
+        <v>-198.4182027536235</v>
       </c>
       <c r="D97">
-        <v>191.4793860967981</v>
+        <v>190.1737972463766</v>
       </c>
       <c r="E97">
-        <v>363.39</v>
+        <v>367.792</v>
       </c>
       <c r="F97">
-        <v>418.19</v>
+        <v>422.592</v>
       </c>
       <c r="G97">
         <v>34</v>
@@ -9223,37 +9223,37 @@
         <v>37.2</v>
       </c>
       <c r="M97">
-        <v>98.60920200000001</v>
+        <v>99.64719360000001</v>
       </c>
       <c r="N97">
-        <v>-61.40920200000001</v>
+        <v>-62.44719360000001</v>
       </c>
       <c r="O97">
-        <v>-15.3523005</v>
+        <v>-15.6117984</v>
       </c>
       <c r="P97">
-        <v>-46.05690150000001</v>
+        <v>-46.83539520000001</v>
       </c>
       <c r="Q97">
-        <v>-43.75690150000001</v>
+        <v>-44.53539520000001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>2.393465427054172</v>
+        <v>2.980381783817716</v>
       </c>
       <c r="T97">
-        <v>22.70371895896946</v>
+        <v>28.37964869871184</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.09431168502915174</v>
+        <v>0.09332927164343141</v>
       </c>
       <c r="W97">
-        <v>0.213561304670126</v>
+        <v>0.2137929577464789</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9261,7 +9261,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.377246740116607</v>
+        <v>0.3733170865737256</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9269,22 +9269,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.3244565107893281</v>
+        <v>0.3263565107893281</v>
       </c>
       <c r="C98">
-        <v>-198.4182027536234</v>
+        <v>-204.1081080449729</v>
       </c>
       <c r="D98">
-        <v>190.1737972463766</v>
+        <v>188.8858919550271</v>
       </c>
       <c r="E98">
-        <v>367.792</v>
+        <v>372.194</v>
       </c>
       <c r="F98">
-        <v>422.592</v>
+        <v>426.994</v>
       </c>
       <c r="G98">
         <v>34</v>
@@ -9305,37 +9305,37 @@
         <v>37.2</v>
       </c>
       <c r="M98">
-        <v>99.64719359999999</v>
+        <v>100.6851852</v>
       </c>
       <c r="N98">
-        <v>-62.44719359999999</v>
+        <v>-63.48518519999999</v>
       </c>
       <c r="O98">
-        <v>-15.6117984</v>
+        <v>-15.8712963</v>
       </c>
       <c r="P98">
-        <v>-46.83539519999999</v>
+        <v>-47.61388889999999</v>
       </c>
       <c r="Q98">
-        <v>-44.5353952</v>
+        <v>-45.31388889999999</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>2.980381783817708</v>
+        <v>3.958575711756945</v>
       </c>
       <c r="T98">
-        <v>28.37964869871176</v>
+        <v>37.83953159828236</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.09332927164343142</v>
+        <v>0.09236711420380841</v>
       </c>
       <c r="W98">
-        <v>0.2137929577464789</v>
+        <v>0.214019834470742</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9343,7 +9343,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3733170865737256</v>
+        <v>0.3694684568152337</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9351,22 +9351,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.3263565107893281</v>
+        <v>0.3282565107893282</v>
       </c>
       <c r="C99">
-        <v>-204.1081080449729</v>
+        <v>-209.780686633201</v>
       </c>
       <c r="D99">
-        <v>188.8858919550271</v>
+        <v>187.6153133667989</v>
       </c>
       <c r="E99">
-        <v>372.194</v>
+        <v>376.5959999999999</v>
       </c>
       <c r="F99">
-        <v>426.994</v>
+        <v>431.396</v>
       </c>
       <c r="G99">
         <v>34</v>
@@ -9387,37 +9387,37 @@
         <v>37.2</v>
       </c>
       <c r="M99">
-        <v>100.6851852</v>
+        <v>101.7231768</v>
       </c>
       <c r="N99">
-        <v>-63.48518519999999</v>
+        <v>-64.52317679999999</v>
       </c>
       <c r="O99">
-        <v>-15.8712963</v>
+        <v>-16.1307942</v>
       </c>
       <c r="P99">
-        <v>-47.61388889999999</v>
+        <v>-48.39238259999999</v>
       </c>
       <c r="Q99">
-        <v>-45.31388889999999</v>
+        <v>-46.09238259999999</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>3.958575711756945</v>
+        <v>5.914963567635418</v>
       </c>
       <c r="T99">
-        <v>37.83953159828236</v>
+        <v>56.75929739742354</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.09236711420380841</v>
+        <v>0.09142459263030017</v>
       </c>
       <c r="W99">
-        <v>0.214019834470742</v>
+        <v>0.2142420810577752</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9425,7 +9425,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3694684568152337</v>
+        <v>0.3656983705212007</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9433,22 +9433,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.3282565107893282</v>
+        <v>0.3301565107893282</v>
       </c>
       <c r="C100">
-        <v>-209.780686633201</v>
+        <v>-215.4362858365652</v>
       </c>
       <c r="D100">
-        <v>187.6153133667989</v>
+        <v>186.3617141634348</v>
       </c>
       <c r="E100">
-        <v>376.5959999999999</v>
+        <v>380.998</v>
       </c>
       <c r="F100">
-        <v>431.396</v>
+        <v>435.798</v>
       </c>
       <c r="G100">
         <v>34</v>
@@ -9469,37 +9469,37 @@
         <v>37.2</v>
       </c>
       <c r="M100">
-        <v>101.7231768</v>
+        <v>102.7611684</v>
       </c>
       <c r="N100">
-        <v>-64.52317679999999</v>
+        <v>-65.5611684</v>
       </c>
       <c r="O100">
-        <v>-16.1307942</v>
+        <v>-16.3902921</v>
       </c>
       <c r="P100">
-        <v>-48.39238259999999</v>
+        <v>-49.1708763</v>
       </c>
       <c r="Q100">
-        <v>-46.09238259999999</v>
+        <v>-46.87087630000001</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>5.914963567635418</v>
+        <v>11.78412713527083</v>
       </c>
       <c r="T100">
-        <v>56.75929739742354</v>
+        <v>113.518594794847</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.09142459263030017</v>
+        <v>0.09050111189666077</v>
       </c>
       <c r="W100">
-        <v>0.2142420810577752</v>
+        <v>0.2144598378147674</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9507,91 +9507,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3656983705212007</v>
+        <v>0.3620044475866431</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.3301565107893282</v>
-      </c>
-      <c r="C101">
-        <v>-215.4362858365652</v>
-      </c>
-      <c r="D101">
-        <v>186.3617141634348</v>
-      </c>
-      <c r="E101">
-        <v>380.998</v>
-      </c>
-      <c r="F101">
-        <v>435.798</v>
-      </c>
-      <c r="G101">
-        <v>34</v>
-      </c>
-      <c r="H101">
-        <v>385.4</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>39.5</v>
-      </c>
-      <c r="K101">
-        <v>2.300000000000001</v>
-      </c>
-      <c r="L101">
-        <v>37.2</v>
-      </c>
-      <c r="M101">
-        <v>102.7611684</v>
-      </c>
-      <c r="N101">
-        <v>-65.5611684</v>
-      </c>
-      <c r="O101">
-        <v>-16.3902921</v>
-      </c>
-      <c r="P101">
-        <v>-49.1708763</v>
-      </c>
-      <c r="Q101">
-        <v>-46.87087630000001</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>11.78412713527083</v>
-      </c>
-      <c r="T101">
-        <v>113.518594794847</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.09050111189666077</v>
-      </c>
-      <c r="W101">
-        <v>0.2144598378147674</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3620044475866431</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
